--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL31" headerRowCount="1">
-  <autoFilter ref="A1:EL31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL37" headerRowCount="1">
+  <autoFilter ref="A1:EL37"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -280,10 +280,10 @@
     <tableColumn id="134" name="pinnacle_ft_over25"/>
     <tableColumn id="135" name="pinnacle_btts_yes"/>
     <tableColumn id="136" name="pinnacle_btts_no"/>
-    <tableColumn id="137" name="pinnacle_1st_half_under15"/>
-    <tableColumn id="138" name="pinnacle_1st_half_over05"/>
-    <tableColumn id="139" name="pinnacle_1st_half_under05"/>
-    <tableColumn id="140" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="137" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="138" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="139" name="pinnacle_1st_half_over05"/>
+    <tableColumn id="140" name="pinnacle_1st_half_under05"/>
     <tableColumn id="141" name="pinnacle_corners_over_85"/>
     <tableColumn id="142" name="pinnacle_corners_under_85"/>
   </tableColumns>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL31"/>
+  <dimension ref="A1:EL37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -719,10 +719,10 @@
     <col width="24" customWidth="1" min="134" max="134"/>
     <col width="22.8" customWidth="1" min="135" max="135"/>
     <col width="21.6" customWidth="1" min="136" max="136"/>
-    <col width="32.4" customWidth="1" min="137" max="137"/>
-    <col width="31.2" customWidth="1" min="138" max="138"/>
-    <col width="32.4" customWidth="1" min="139" max="139"/>
-    <col width="31.2" customWidth="1" min="140" max="140"/>
+    <col width="31.2" customWidth="1" min="137" max="137"/>
+    <col width="32.4" customWidth="1" min="138" max="138"/>
+    <col width="31.2" customWidth="1" min="139" max="139"/>
+    <col width="32.4" customWidth="1" min="140" max="140"/>
     <col width="31.2" customWidth="1" min="141" max="141"/>
     <col width="32.4" customWidth="1" min="142" max="142"/>
   </cols>
@@ -1410,22 +1410,22 @@
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_1st_half_over15</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_1st_half_under15</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_1st_half_over05</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_1st_half_under05</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over15</t>
         </is>
       </c>
       <c r="EK1" s="1" t="inlineStr">
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -2255,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -3218,22 +3218,22 @@
       </c>
       <c r="EG5" t="inlineStr">
         <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="EH5" t="inlineStr">
+      <c r="EI5" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="EI5" t="inlineStr">
+      <c r="EJ5" t="inlineStr">
         <is>
           <t>2.74</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>3.33</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="EG6" t="inlineStr">
         <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="EH6" t="inlineStr">
+      <c r="EI6" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="EI6" t="inlineStr">
+      <c r="EJ6" t="inlineStr">
         <is>
           <t>3.02</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>2.97</t>
         </is>
       </c>
       <c r="EK6" t="inlineStr">
@@ -3719,254 +3719,254 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>46050.95833333334</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
         <v>14</v>
       </c>
-      <c r="L7" t="n">
-        <v>15</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="X7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Estádio Urbano Caldeira</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD7" t="n">
         <v>5</v>
       </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>20</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>25</v>
-      </c>
-      <c r="W7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Arena Condá</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Rua Clevelândia, Bairro Centro, Chapecó, Santa Catarina</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3</v>
-      </c>
       <c r="AE7" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>3.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
         <v>1</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>626</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>13577</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>4</v>
       </c>
-      <c r="BA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>623</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>17551</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12</v>
-      </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL7" t="n">
         <v>2</v>
       </c>
       <c r="BM7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BN7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
         <v>1</v>
       </c>
       <c r="BV7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BW7" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="BX7" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BY7" t="n">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.84</v>
+        <v>1.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.13</v>
+        <v>2.76</v>
       </c>
       <c r="CC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG7" t="n">
         <v>0</v>
@@ -3990,40 +3990,40 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
         <v>1</v>
       </c>
       <c r="CR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV7" t="n">
         <v>13</v>
       </c>
-      <c r="CS7" t="n">
-        <v>31</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>4</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>10</v>
-      </c>
       <c r="CW7" t="n">
         <v>1</v>
       </c>
       <c r="CX7" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="CY7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CZ7" t="n">
         <v>0</v>
@@ -4038,10 +4038,10 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
@@ -4083,81 +4083,73 @@
         <v>1</v>
       </c>
       <c r="DS7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="b">
         <v>1</v>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EG7" t="inlineStr"/>
       <c r="EH7" t="inlineStr"/>
       <c r="EI7" t="inlineStr"/>
       <c r="EJ7" t="inlineStr"/>
-      <c r="EK7" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EL7" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
+      <c r="EK7" t="inlineStr"/>
+      <c r="EL7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4175,164 +4167,164 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
         <v>46050.95833333334</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="X8" t="n">
         <v>5</v>
       </c>
-      <c r="R8" t="n">
-        <v>6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>14</v>
-      </c>
       <c r="Y8" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Estádio Urbano Caldeira</t>
+          <t>Arena Condá</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+          <t>Rua Clevelândia, Bairro Centro, Chapecó, Santa Catarina</t>
         </is>
       </c>
       <c r="AC8" t="n">
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>1</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
@@ -4344,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>13577</v>
+        <v>17551</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
@@ -4353,134 +4345,134 @@
         <v>1</v>
       </c>
       <c r="BI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>151</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="n">
         <v>4</v>
       </c>
-      <c r="BK8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR8" t="n">
+      <c r="CV8" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>18</v>
+      </c>
+      <c r="CY8" t="n">
         <v>4</v>
       </c>
-      <c r="BS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>19</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>87</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>10</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>32</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ8" t="n">
         <v>0</v>
       </c>
@@ -4494,10 +4486,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DE8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4539,73 +4531,81 @@
         <v>1</v>
       </c>
       <c r="DS8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV8" t="b">
         <v>1</v>
       </c>
       <c r="DW8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="DX8" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DY8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="DZ8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EA8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EB8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr"/>
       <c r="EH8" t="inlineStr"/>
       <c r="EI8" t="inlineStr"/>
       <c r="EJ8" t="inlineStr"/>
-      <c r="EK8" t="inlineStr"/>
-      <c r="EL8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5050,22 +5050,22 @@
       </c>
       <c r="EG9" t="inlineStr">
         <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="EH9" t="inlineStr">
+      <c r="EI9" t="inlineStr">
         <is>
           <t>1.60</t>
         </is>
       </c>
-      <c r="EI9" t="inlineStr">
+      <c r="EJ9" t="inlineStr">
         <is>
           <t>2.37</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>3.27</t>
         </is>
       </c>
       <c r="EK9" t="inlineStr"/>
@@ -5962,22 +5962,22 @@
       </c>
       <c r="EG11" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="EH11" t="inlineStr">
+      <c r="EI11" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EI11" t="inlineStr">
+      <c r="EJ11" t="inlineStr">
         <is>
           <t>2.63</t>
-        </is>
-      </c>
-      <c r="EJ11" t="inlineStr">
-        <is>
-          <t>3.40</t>
         </is>
       </c>
       <c r="EK11" t="inlineStr"/>
@@ -6418,22 +6418,22 @@
       </c>
       <c r="EG12" t="inlineStr">
         <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EH12" t="inlineStr">
+      <c r="EI12" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EI12" t="inlineStr">
+      <c r="EJ12" t="inlineStr">
         <is>
           <t>3.27</t>
-        </is>
-      </c>
-      <c r="EJ12" t="inlineStr">
-        <is>
-          <t>2.76</t>
         </is>
       </c>
       <c r="EK12" t="inlineStr"/>
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6799,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6874,22 +6874,22 @@
       </c>
       <c r="EG13" t="inlineStr">
         <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="EH13" t="inlineStr">
+      <c r="EI13" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="EI13" t="inlineStr">
+      <c r="EJ13" t="inlineStr">
         <is>
           <t>2.71</t>
-        </is>
-      </c>
-      <c r="EJ13" t="inlineStr">
-        <is>
-          <t>3.43</t>
         </is>
       </c>
       <c r="EK13" t="inlineStr"/>
@@ -6911,146 +6911,146 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>46057.95833333334</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" t="n">
         <v>11</v>
       </c>
-      <c r="M14" t="n">
-        <v>5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>9</v>
-      </c>
       <c r="T14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V14" t="n">
         <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X14" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="Z14" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Estádio Urbano Caldeira</t>
+          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -7059,13 +7059,13 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
         <v>-1</v>
@@ -7092,61 +7092,61 @@
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
         <v>1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU14" t="n">
         <v>1</v>
       </c>
       <c r="BV14" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BW14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BX14" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="BY14" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="CB14" t="n">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
@@ -7173,16 +7173,16 @@
         <v>1</v>
       </c>
       <c r="CK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO14" t="n">
         <v>0</v>
@@ -7194,16 +7194,16 @@
         <v>1</v>
       </c>
       <c r="CR14" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CS14" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="CT14" t="n">
         <v>1</v>
       </c>
       <c r="CU14" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="CV14" t="n">
         <v>15</v>
@@ -7212,10 +7212,10 @@
         <v>1</v>
       </c>
       <c r="CX14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CZ14" t="n">
         <v>0</v>
@@ -7272,10 +7272,10 @@
         <v>1</v>
       </c>
       <c r="DR14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT14" t="b">
         <v>0</v>
@@ -7288,72 +7288,72 @@
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="DX14" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="DZ14" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EA14" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EB14" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EC14" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="ED14" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="EE14" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EF14" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EG14" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EI14" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
       <c r="EJ14" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EK14" t="inlineStr"/>
@@ -7375,40 +7375,40 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
         <v>46057.95833333334</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -7417,104 +7417,104 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" t="n">
         <v>5</v>
       </c>
-      <c r="S15" t="n">
-        <v>11</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
       <c r="U15" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V15" t="n">
         <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X15" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="Z15" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
+          <t>Estádio Urbano Caldeira</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL15" t="n">
         <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AO15" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -7523,13 +7523,13 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB15" t="n">
         <v>-1</v>
@@ -7556,61 +7556,61 @@
         <v>2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP15" t="n">
         <v>1</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU15" t="n">
         <v>1</v>
       </c>
       <c r="BV15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW15" t="n">
         <v>13</v>
       </c>
-      <c r="BW15" t="n">
-        <v>19</v>
-      </c>
       <c r="BX15" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="BY15" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="CB15" t="n">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
@@ -7637,16 +7637,16 @@
         <v>1</v>
       </c>
       <c r="CK15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
@@ -7658,16 +7658,16 @@
         <v>1</v>
       </c>
       <c r="CR15" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="CS15" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT15" t="n">
         <v>1</v>
       </c>
       <c r="CU15" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="CV15" t="n">
         <v>15</v>
@@ -7676,10 +7676,10 @@
         <v>1</v>
       </c>
       <c r="CX15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CZ15" t="n">
         <v>0</v>
@@ -7697,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="DE15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7736,10 +7736,10 @@
         <v>1</v>
       </c>
       <c r="DR15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="b">
         <v>0</v>
@@ -7752,72 +7752,72 @@
       </c>
       <c r="DW15" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="DX15" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="DY15" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="DZ15" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EA15" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EB15" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EC15" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="ED15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EE15" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EF15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EG15" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EH15" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI15" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EJ15" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EK15" t="inlineStr"/>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -7854,25 +7854,25 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -7887,251 +7887,251 @@
         <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
         <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V16" t="n">
         <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="Z16" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Arena do Grêmio</t>
+          <t>Allianz Parque</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
+          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.82</v>
+        <v>7.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AL16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>619</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8953</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>1.91</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>616</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW16" t="n">
+      <c r="CA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR16" t="n">
         <v>17</v>
       </c>
-      <c r="BX16" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>77</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>9</v>
-      </c>
       <c r="CS16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV16" t="n">
         <v>13</v>
@@ -8140,10 +8140,10 @@
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CY16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI16" t="n">
         <v>3</v>
@@ -8216,68 +8216,68 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="DZ16" t="inlineStr"/>
-      <c r="EA16" t="inlineStr"/>
+          <t>10.32</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr"/>
+      <c r="EJ16" t="inlineStr"/>
+      <c r="EK16" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EJ16" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="EK16" t="inlineStr"/>
-      <c r="EL16" t="inlineStr"/>
+      <c r="EL16" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8310,25 +8310,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
         <v>6</v>
       </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>10</v>
-      </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -8343,116 +8343,116 @@
         <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
         <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V17" t="n">
         <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Allianz Parque</t>
+          <t>Arena do Grêmio</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
+          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX17" t="n">
         <v>4</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2</v>
-      </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
         <v>3</v>
       </c>
       <c r="BB17" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>8953</v>
+        <v>-1</v>
       </c>
       <c r="BG17" t="n">
         <v>2</v>
@@ -8473,25 +8473,25 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL17" t="n">
         <v>2</v>
       </c>
       <c r="BM17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BN17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
         <v>1</v>
@@ -8500,46 +8500,46 @@
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BW17" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="BX17" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="BY17" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN17" t="n">
         <v>0</v>
@@ -8572,22 +8572,22 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ17" t="n">
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CS17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV17" t="n">
         <v>13</v>
@@ -8596,10 +8596,10 @@
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CY17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
         <v>3</v>
@@ -8672,68 +8672,68 @@
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>10.32</t>
-        </is>
-      </c>
-      <c r="DZ17" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EA17" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="DZ17" t="inlineStr"/>
+      <c r="EA17" t="inlineStr"/>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr"/>
-      <c r="EH17" t="inlineStr"/>
-      <c r="EI17" t="inlineStr"/>
-      <c r="EJ17" t="inlineStr"/>
-      <c r="EK17" t="inlineStr">
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="EL17" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr"/>
+      <c r="EL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9073,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="DE18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9178,22 +9178,22 @@
       </c>
       <c r="EG18" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="EH18" t="inlineStr">
+      <c r="EI18" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="EI18" t="inlineStr">
+      <c r="EJ18" t="inlineStr">
         <is>
           <t>2.88</t>
-        </is>
-      </c>
-      <c r="EJ18" t="inlineStr">
-        <is>
-          <t>3.18</t>
         </is>
       </c>
       <c r="EK18" t="inlineStr">
@@ -9982,7 +9982,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DE20" t="n">
         <v>2</v>
@@ -10015,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10982,22 +10982,22 @@
       </c>
       <c r="EG22" t="inlineStr">
         <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EH22" t="inlineStr">
+      <c r="EI22" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="EI22" t="inlineStr">
+      <c r="EJ22" t="inlineStr">
         <is>
           <t>2.80</t>
-        </is>
-      </c>
-      <c r="EJ22" t="inlineStr">
-        <is>
-          <t>3.27</t>
         </is>
       </c>
       <c r="EK22" t="inlineStr"/>
@@ -11446,22 +11446,22 @@
       </c>
       <c r="EG23" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
           <t>1.38</t>
         </is>
       </c>
-      <c r="EH23" t="inlineStr">
+      <c r="EI23" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="EI23" t="inlineStr">
+      <c r="EJ23" t="inlineStr">
         <is>
           <t>2.88</t>
-        </is>
-      </c>
-      <c r="EJ23" t="inlineStr">
-        <is>
-          <t>3.18</t>
         </is>
       </c>
       <c r="EK23" t="inlineStr">
@@ -11835,7 +11835,7 @@
         <v>2.47</v>
       </c>
       <c r="DO24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11910,22 +11910,22 @@
       </c>
       <c r="EG24" t="inlineStr">
         <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EH24" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="EH24" t="inlineStr">
+      <c r="EI24" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="EI24" t="inlineStr">
+      <c r="EJ24" t="inlineStr">
         <is>
           <t>3.22</t>
-        </is>
-      </c>
-      <c r="EJ24" t="inlineStr">
-        <is>
-          <t>2.79</t>
         </is>
       </c>
       <c r="EK24" t="inlineStr"/>
@@ -12299,7 +12299,7 @@
         <v>2.3</v>
       </c>
       <c r="DO25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12830,22 +12830,22 @@
       </c>
       <c r="EG26" t="inlineStr">
         <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="EH26" t="inlineStr">
+      <c r="EI26" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="EI26" t="inlineStr">
+      <c r="EJ26" t="inlineStr">
         <is>
           <t>3.18</t>
-        </is>
-      </c>
-      <c r="EJ26" t="inlineStr">
-        <is>
-          <t>2.80</t>
         </is>
       </c>
       <c r="EK26" t="inlineStr">
@@ -13294,22 +13294,22 @@
       </c>
       <c r="EG27" t="inlineStr">
         <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EH27" t="inlineStr">
+        <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="EH27" t="inlineStr">
+      <c r="EI27" t="inlineStr">
         <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EI27" t="inlineStr">
+      <c r="EJ27" t="inlineStr">
         <is>
           <t>2.76</t>
-        </is>
-      </c>
-      <c r="EJ27" t="inlineStr">
-        <is>
-          <t>3.28</t>
         </is>
       </c>
       <c r="EK27" t="inlineStr"/>
@@ -14131,7 +14131,7 @@
         <v>4.58</v>
       </c>
       <c r="DO29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14571,7 +14571,7 @@
         <v>3.67</v>
       </c>
       <c r="DO30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14981,7 +14981,7 @@
         <v>1.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15011,7 +15011,7 @@
         <v>1.51</v>
       </c>
       <c r="DO31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15086,24 +15086,24 @@
       </c>
       <c r="EG31" t="inlineStr">
         <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EH31" t="inlineStr">
+        <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="EH31" t="inlineStr">
+      <c r="EI31" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="EI31" t="inlineStr">
+      <c r="EJ31" t="inlineStr">
         <is>
           <t>2.63</t>
         </is>
       </c>
-      <c r="EJ31" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
       <c r="EK31" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -15114,6 +15114,2758 @@
           <t>2.50</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>46078.91666666666</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>12</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>18</v>
+      </c>
+      <c r="W32" t="n">
+        <v>16</v>
+      </c>
+      <c r="X32" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW32" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX32" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY32" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI32" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK32" t="n">
+        <v>100</v>
+      </c>
+      <c r="DL32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DM32" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="DN32" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DO32" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU32" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV32" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW32" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="DX32" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="DY32" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="DZ32" t="inlineStr"/>
+      <c r="EA32" t="inlineStr"/>
+      <c r="EB32" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC32" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="ED32" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EE32" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF32" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EG32" t="inlineStr"/>
+      <c r="EH32" t="inlineStr"/>
+      <c r="EI32" t="inlineStr"/>
+      <c r="EJ32" t="inlineStr"/>
+      <c r="EK32" t="inlineStr"/>
+      <c r="EL32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>46078.91666666666</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" t="n">
+        <v>12</v>
+      </c>
+      <c r="L33" t="n">
+        <v>19</v>
+      </c>
+      <c r="M33" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>14</v>
+      </c>
+      <c r="U33" t="n">
+        <v>12</v>
+      </c>
+      <c r="V33" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" t="n">
+        <v>14</v>
+      </c>
+      <c r="X33" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
+        </is>
+      </c>
+      <c r="AC33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY33" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DI33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ33" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DM33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DN33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DO33" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP33" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ33" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR33" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS33" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT33" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU33" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV33" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW33" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="DX33" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="DY33" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DZ33" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA33" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EB33" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EG33" t="inlineStr"/>
+      <c r="EH33" t="inlineStr"/>
+      <c r="EI33" t="inlineStr"/>
+      <c r="EJ33" t="inlineStr"/>
+      <c r="EK33" t="inlineStr"/>
+      <c r="EL33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>46078.9375</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>7</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>16</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>18</v>
+      </c>
+      <c r="V34" t="n">
+        <v>9</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Estádio Major Antônio Couto Pereira</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>618</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>27515</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV34" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW34" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX34" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY34" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CB34" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR34" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS34" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU34" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV34" t="n">
+        <v>4</v>
+      </c>
+      <c r="CW34" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX34" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY34" t="n">
+        <v>13</v>
+      </c>
+      <c r="CZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC34" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE34" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DI34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK34" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL34" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DM34" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DN34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DO34" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP34" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV34" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW34" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="DX34" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="DY34" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="DZ34" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EA34" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EB34" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC34" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG34" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>46078.95833333334</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>11</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4</v>
+      </c>
+      <c r="W35" t="n">
+        <v>15</v>
+      </c>
+      <c r="X35" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>52</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Estádio Governador Magalhães Pinto</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Avenida Antonio Abrahão Carã 1001, Pampulhas, Belo Horizonte, Minas Gerais</t>
+        </is>
+      </c>
+      <c r="AC35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV35" t="n">
+        <v>13</v>
+      </c>
+      <c r="BW35" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX35" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY35" t="n">
+        <v>90</v>
+      </c>
+      <c r="BZ35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CA35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CB35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR35" t="n">
+        <v>21</v>
+      </c>
+      <c r="CS35" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU35" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV35" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW35" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX35" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY35" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ35" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA35" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB35" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC35" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE35" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG35" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI35" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ35" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK35" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DM35" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DN35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="DO35" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR35" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS35" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT35" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU35" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV35" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW35" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="DX35" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="DY35" t="inlineStr">
+        <is>
+          <t>5.49</t>
+        </is>
+      </c>
+      <c r="DZ35" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EA35" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="EB35" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC35" t="inlineStr">
+        <is>
+          <t>3.99</t>
+        </is>
+      </c>
+      <c r="ED35" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EE35" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EF35" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG35" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EH35" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI35" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ35" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EK35" t="inlineStr"/>
+      <c r="EL35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46079.02083333334</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>9</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>11</v>
+      </c>
+      <c r="T36" t="n">
+        <v>6</v>
+      </c>
+      <c r="U36" t="n">
+        <v>18</v>
+      </c>
+      <c r="V36" t="n">
+        <v>8</v>
+      </c>
+      <c r="W36" t="n">
+        <v>12</v>
+      </c>
+      <c r="X36" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Arena do Grêmio</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>616</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>15714</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>71</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>32</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>126</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR36" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS36" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU36" t="n">
+        <v>5</v>
+      </c>
+      <c r="CV36" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY36" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ36" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA36" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB36" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC36" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD36" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF36" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI36" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DJ36" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK36" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DM36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DN36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DO36" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP36" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ36" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR36" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS36" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT36" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU36" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV36" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW36" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="DX36" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="DY36" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="DZ36" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EA36" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB36" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EC36" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="ED36" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EE36" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF36" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EG36" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EH36" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI36" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ36" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="EK36" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EL36" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>46079.02083333334</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>11</v>
+      </c>
+      <c r="L37" t="n">
+        <v>16</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7</v>
+      </c>
+      <c r="S37" t="n">
+        <v>7</v>
+      </c>
+      <c r="T37" t="n">
+        <v>11</v>
+      </c>
+      <c r="U37" t="n">
+        <v>13</v>
+      </c>
+      <c r="V37" t="n">
+        <v>18</v>
+      </c>
+      <c r="W37" t="n">
+        <v>14</v>
+      </c>
+      <c r="X37" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Allianz Parque</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>619</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>10329</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV37" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW37" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX37" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY37" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CA37" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CB37" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="CC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR37" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS37" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU37" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV37" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW37" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX37" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY37" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA37" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC37" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD37" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF37" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DI37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DJ37" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="DM37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DN37" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="DO37" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP37" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ37" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR37" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU37" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV37" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW37" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="DX37" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="DY37" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="DZ37" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA37" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EB37" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC37" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EE37" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EF37" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EG37" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EK37" t="inlineStr"/>
+      <c r="EL37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL37" headerRowCount="1">
-  <autoFilter ref="A1:EL37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL38" headerRowCount="1">
+  <autoFilter ref="A1:EL38"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL37"/>
+  <dimension ref="A1:EL38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -1903,164 +1903,156 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
         <v>46050.91666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>10</v>
-      </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>14</v>
+      </c>
+      <c r="X3" t="n">
         <v>20</v>
       </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>30</v>
-      </c>
-      <c r="W3" t="n">
-        <v>9</v>
-      </c>
-      <c r="X3" t="n">
-        <v>19</v>
-      </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="Z3" t="n">
-        <v>71</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Estádio Major Antônio Couto Pereira</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.21</v>
+        <v>3.2</v>
       </c>
       <c r="AF3" t="n">
         <v>3.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="AJ3" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="n">
         <v>1</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>635</v>
+        <v>-1</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -2072,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>19535</v>
+        <v>25770</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
@@ -2081,133 +2073,133 @@
         <v>1</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ3" t="n">
         <v>2</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BM3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BO3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BS3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU3" t="n">
         <v>1</v>
       </c>
       <c r="BV3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>97</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR3" t="n">
         <v>17</v>
       </c>
-      <c r="BW3" t="n">
-        <v>69</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>74</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR3" t="n">
+      <c r="CS3" t="n">
         <v>10</v>
       </c>
-      <c r="CS3" t="n">
-        <v>24</v>
-      </c>
       <c r="CT3" t="n">
         <v>1</v>
       </c>
       <c r="CU3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="CV3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CW3" t="n">
         <v>1</v>
       </c>
       <c r="CX3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="CY3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="CZ3" t="n">
         <v>0</v>
@@ -2222,10 +2214,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2261,13 +2253,13 @@
         <v>1</v>
       </c>
       <c r="DQ3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT3" t="b">
         <v>0</v>
@@ -2276,64 +2268,72 @@
         <v>0</v>
       </c>
       <c r="DV3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="DZ3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EA3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EG3" t="inlineStr"/>
       <c r="EH3" t="inlineStr"/>
       <c r="EI3" t="inlineStr"/>
       <c r="EJ3" t="inlineStr"/>
-      <c r="EK3" t="inlineStr"/>
-      <c r="EL3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2366,78 +2366,86 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>7</v>
       </c>
-      <c r="L4" t="n">
-        <v>12</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="U4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" t="n">
         <v>14</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>13</v>
       </c>
-      <c r="W4" t="n">
-        <v>14</v>
-      </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Estádio Manoel Barradas</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Rua Artêmio Castro Valente 1, Bairro Nossa Senhora da Vitória, Salvador, Bahia</t>
+        </is>
+      </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.34</v>
+        <v>4.64</v>
       </c>
       <c r="AH4" t="n">
         <v>1.36</v>
@@ -2446,208 +2454,208 @@
         <v>2.21</v>
       </c>
       <c r="AJ4" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>610</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>16511</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS4" t="n">
         <v>4</v>
       </c>
-      <c r="AK4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>25770</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN4" t="n">
+      <c r="BT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX4" t="n">
         <v>9</v>
       </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>97</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>63</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV4" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX4" t="n">
-        <v>7</v>
-      </c>
       <c r="CY4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ4" t="n">
         <v>0</v>
@@ -2662,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DE4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2695,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -2704,10 +2712,10 @@
         <v>1</v>
       </c>
       <c r="DR4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT4" t="b">
         <v>0</v>
@@ -2716,33 +2724,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EA4" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
       <c r="EB4" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -2750,38 +2750,46 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr"/>
-      <c r="EH4" t="inlineStr"/>
-      <c r="EI4" t="inlineStr"/>
-      <c r="EJ4" t="inlineStr"/>
-      <c r="EK4" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2799,143 +2807,143 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
         <v>46050.91666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="W5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="Z5" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Estádio Manoel Barradas</t>
+          <t>Estádio Major Antônio Couto Pereira</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Rua Artêmio Castro Valente 1, Bairro Nossa Senhora da Vitória, Salvador, Bahia</t>
+          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.64</v>
+        <v>3.05</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.82</v>
+        <v>4.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AL5" t="n">
         <v>1.75</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.55</v>
+        <v>3.04</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2944,19 +2952,19 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>610</v>
+        <v>635</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
@@ -2968,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>16511</v>
+        <v>19535</v>
       </c>
       <c r="BG5" t="n">
         <v>2</v>
@@ -2977,22 +2985,22 @@
         <v>1</v>
       </c>
       <c r="BI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM5" t="n">
         <v>2</v>
       </c>
       <c r="BN5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BO5" t="n">
         <v>2</v>
@@ -3004,37 +3012,37 @@
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BS5" t="n">
         <v>4</v>
       </c>
       <c r="BT5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU5" t="n">
         <v>1</v>
       </c>
       <c r="BV5" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="BW5" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="BX5" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="BY5" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.99</v>
+        <v>0.78</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.17</v>
+        <v>3.08</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.16</v>
+        <v>3.86</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
@@ -3082,28 +3090,28 @@
         <v>1</v>
       </c>
       <c r="CR5" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU5" t="n">
         <v>19</v>
       </c>
-      <c r="CS5" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>17</v>
-      </c>
       <c r="CV5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="CW5" t="n">
         <v>1</v>
       </c>
       <c r="CX5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="CY5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ5" t="n">
         <v>0</v>
@@ -3118,11 +3126,11 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
         <v>1.5</v>
       </c>
-      <c r="DE5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="DF5" t="n">
         <v>0</v>
       </c>
@@ -3151,13 +3159,13 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
       </c>
       <c r="DQ5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="b">
         <v>0</v>
@@ -3176,66 +3184,58 @@
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="DZ5" t="inlineStr"/>
-      <c r="EA5" t="inlineStr"/>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
       <c r="EK5" t="inlineStr"/>
       <c r="EL5" t="inlineStr"/>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -6014,22 +6014,22 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -6044,312 +6044,312 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="Z12" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
       </c>
       <c r="AE12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1.41</v>
       </c>
-      <c r="AF12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AN12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>635</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>88</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>2.01</v>
       </c>
-      <c r="AL12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB12" t="n">
+      <c r="CA12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
         <v>-1</v>
       </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>56421</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM12" t="n">
+      <c r="CN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
         <v>4</v>
       </c>
-      <c r="BN12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>57</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>16</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>156</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>77</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>8</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>17</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>20</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>12</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>3</v>
-      </c>
       <c r="DP12" t="b">
         <v>1</v>
       </c>
       <c r="DQ12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="b">
         <v>0</v>
@@ -6364,76 +6364,76 @@
         <v>0</v>
       </c>
       <c r="DV12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="DX12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="DY12" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="DZ12" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EA12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EB12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EC12" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.49</t>
         </is>
       </c>
       <c r="ED12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EE12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EF12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EH12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EJ12" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="EK12" t="inlineStr"/>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -6470,22 +6470,22 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
@@ -6500,111 +6500,111 @@
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="Z13" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
         <v>2</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.41</v>
       </c>
       <c r="AF13" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.65</v>
+        <v>1.99</v>
       </c>
       <c r="AO13" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.23</v>
+        <v>2.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.56</v>
+        <v>3.04</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA13" t="n">
         <v>1</v>
       </c>
       <c r="BB13" t="n">
-        <v>635</v>
+        <v>-1</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
@@ -6616,82 +6616,82 @@
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-1</v>
+        <v>56421</v>
       </c>
       <c r="BG13" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH13" t="n">
         <v>1</v>
       </c>
       <c r="BI13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BK13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BM13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN13" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ13" t="n">
         <v>2</v>
       </c>
       <c r="BR13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS13" t="n">
         <v>1</v>
       </c>
       <c r="BT13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU13" t="n">
         <v>1</v>
       </c>
       <c r="BV13" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="BW13" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="BX13" t="n">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="BY13" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD13" t="n">
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
@@ -6715,43 +6715,43 @@
         <v>0</v>
       </c>
       <c r="CM13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ13" t="n">
         <v>1</v>
       </c>
       <c r="CR13" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="CS13" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="CT13" t="n">
         <v>1</v>
       </c>
       <c r="CU13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="CV13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CW13" t="n">
         <v>1</v>
       </c>
       <c r="CX13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CZ13" t="n">
         <v>0</v>
@@ -6766,10 +6766,10 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF13" t="n">
         <v>0</v>
@@ -6778,10 +6778,10 @@
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ13" t="n">
         <v>0</v>
@@ -6799,13 +6799,13 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
       </c>
       <c r="DQ13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR13" t="b">
         <v>0</v>
@@ -6820,76 +6820,76 @@
         <v>0</v>
       </c>
       <c r="DV13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="DX13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="DY13" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>7.38</t>
         </is>
       </c>
       <c r="DZ13" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EA13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EB13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EC13" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="ED13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EE13" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EF13" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG13" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EH13" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EJ13" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EK13" t="inlineStr"/>
@@ -6911,40 +6911,40 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
         <v>46057.95833333334</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -6953,104 +6953,104 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>9</v>
+      </c>
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="S14" t="n">
-        <v>11</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
       <c r="U14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X14" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Y14" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="Z14" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
+          <t>Estádio Urbano Caldeira</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL14" t="n">
         <v>1.85</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AO14" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.31</v>
+        <v>2.07</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -7059,13 +7059,13 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB14" t="n">
         <v>-1</v>
@@ -7092,61 +7092,61 @@
         <v>2</v>
       </c>
       <c r="BJ14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP14" t="n">
         <v>1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BT14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU14" t="n">
         <v>1</v>
       </c>
       <c r="BV14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW14" t="n">
         <v>13</v>
       </c>
-      <c r="BW14" t="n">
-        <v>19</v>
-      </c>
       <c r="BX14" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="BY14" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="CB14" t="n">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
@@ -7173,16 +7173,16 @@
         <v>1</v>
       </c>
       <c r="CK14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
         <v>0</v>
@@ -7194,16 +7194,16 @@
         <v>1</v>
       </c>
       <c r="CR14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="CS14" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="CT14" t="n">
         <v>1</v>
       </c>
       <c r="CU14" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="CV14" t="n">
         <v>15</v>
@@ -7212,10 +7212,10 @@
         <v>1</v>
       </c>
       <c r="CX14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="CZ14" t="n">
         <v>0</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DE14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7272,10 +7272,10 @@
         <v>1</v>
       </c>
       <c r="DR14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="b">
         <v>0</v>
@@ -7288,72 +7288,72 @@
       </c>
       <c r="DW14" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="DX14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="DY14" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="DZ14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EA14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EB14" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EC14" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="ED14" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="EE14" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EF14" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EG14" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EH14" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EI14" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EJ14" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EK14" t="inlineStr"/>
@@ -7375,146 +7375,146 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
         <v>46057.95833333334</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
+        <v>8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
         <v>11</v>
       </c>
-      <c r="M15" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3</v>
-      </c>
-      <c r="S15" t="n">
-        <v>9</v>
-      </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V15" t="n">
         <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="Z15" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Estádio Urbano Caldeira</t>
+          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.21</v>
+        <v>2.59</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
         <v>1.85</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AO15" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AU15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -7523,13 +7523,13 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB15" t="n">
         <v>-1</v>
@@ -7556,61 +7556,61 @@
         <v>2</v>
       </c>
       <c r="BJ15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BO15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
         <v>1</v>
       </c>
       <c r="BQ15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BT15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU15" t="n">
         <v>1</v>
       </c>
       <c r="BV15" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BW15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BX15" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="BY15" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="n">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
@@ -7637,16 +7637,16 @@
         <v>1</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
@@ -7658,16 +7658,16 @@
         <v>1</v>
       </c>
       <c r="CR15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="CS15" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="CT15" t="n">
         <v>1</v>
       </c>
       <c r="CU15" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="CV15" t="n">
         <v>15</v>
@@ -7676,10 +7676,10 @@
         <v>1</v>
       </c>
       <c r="CX15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CZ15" t="n">
         <v>0</v>
@@ -7697,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="DE15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7736,10 +7736,10 @@
         <v>1</v>
       </c>
       <c r="DR15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT15" t="b">
         <v>0</v>
@@ -7752,72 +7752,72 @@
       </c>
       <c r="DW15" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="DX15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DY15" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="DZ15" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EA15" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EB15" t="inlineStr">
         <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC15" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EF15" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EG15" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr">
+        <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="EC15" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="ED15" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="EE15" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="EF15" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EG15" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EH15" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EI15" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
       <c r="EJ15" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EK15" t="inlineStr"/>
@@ -13219,7 +13219,7 @@
         <v>2.3</v>
       </c>
       <c r="DO27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -15131,12 +15131,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -15152,111 +15152,119 @@
         <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
+        <v>12</v>
+      </c>
+      <c r="L32" t="n">
+        <v>19</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>7</v>
       </c>
-      <c r="L32" t="n">
-        <v>9</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3</v>
-      </c>
       <c r="R32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V32" t="n">
         <v>18</v>
       </c>
       <c r="W32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X32" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Z32" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
+        </is>
+      </c>
       <c r="AC32" t="n">
         <v>5</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO32" t="n">
         <v>2.3</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>3</v>
-      </c>
       <c r="AP32" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR32" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AU32" t="n">
         <v>2</v>
@@ -15265,19 +15273,19 @@
         <v>1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX32" t="n">
         <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB32" t="n">
         <v>-1</v>
@@ -15286,13 +15294,13 @@
         <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE32" t="n">
         <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>-1</v>
+        <v>21687</v>
       </c>
       <c r="BG32" t="n">
         <v>2</v>
@@ -15304,61 +15312,61 @@
         <v>2</v>
       </c>
       <c r="BJ32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT32" t="n">
         <v>5</v>
       </c>
-      <c r="BM32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ32" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT32" t="n">
-        <v>3</v>
-      </c>
       <c r="BU32" t="n">
         <v>1</v>
       </c>
       <c r="BV32" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="BW32" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="BX32" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BY32" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0.89</v>
+        <v>1.38</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="CC32" t="n">
         <v>0</v>
@@ -15388,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="CL32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM32" t="n">
         <v>1</v>
@@ -15406,73 +15414,73 @@
         <v>1</v>
       </c>
       <c r="CR32" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CS32" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="CT32" t="n">
         <v>1</v>
       </c>
       <c r="CU32" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV32" t="n">
         <v>16</v>
       </c>
-      <c r="CV32" t="n">
-        <v>18</v>
-      </c>
       <c r="CW32" t="n">
         <v>1</v>
       </c>
       <c r="CX32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CY32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CZ32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DB32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC32" t="n">
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DE32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DF32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DG32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DH32" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DI32" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="DJ32" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DL32" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="DM32" t="n">
-        <v>0.66</v>
+        <v>1.04</v>
       </c>
       <c r="DN32" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="DO32" t="n">
         <v>4</v>
@@ -15500,44 +15508,52 @@
       </c>
       <c r="DW32" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="DX32" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="DY32" t="inlineStr">
         <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="DZ32" t="inlineStr"/>
-      <c r="EA32" t="inlineStr"/>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DZ32" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA32" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
       <c r="EB32" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EC32" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="ED32" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EE32" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EF32" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EG32" t="inlineStr"/>
@@ -15563,12 +15579,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -15584,119 +15600,111 @@
         <v>2</v>
       </c>
       <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
         <v>7</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
+        <v>9</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
         <v>12</v>
       </c>
-      <c r="L33" t="n">
-        <v>19</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
+      <c r="U33" t="n">
         <v>7</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>14</v>
-      </c>
-      <c r="U33" t="n">
-        <v>12</v>
       </c>
       <c r="V33" t="n">
         <v>18</v>
       </c>
       <c r="W33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y33" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Z33" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AU33" t="n">
         <v>2</v>
@@ -15705,19 +15713,19 @@
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" t="n">
         <v>-1</v>
@@ -15726,7 +15734,7 @@
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -15735,184 +15743,184 @@
         <v>-1</v>
       </c>
       <c r="BG33" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BH33" t="n">
         <v>1</v>
       </c>
       <c r="BI33" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BJ33" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BK33" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BL33" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BM33" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BN33" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BO33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
         <v>4</v>
       </c>
-      <c r="BR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>1</v>
-      </c>
       <c r="BT33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY33" t="n">
         <v>5</v>
       </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>51</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>106</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CB33" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="CC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CN33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DB33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC33" t="n">
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DE33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DF33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DG33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH33" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DI33" t="n">
-        <v>0.33</v>
+        <v>2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="DN33" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="DO33" t="n">
         <v>4</v>
@@ -15940,52 +15948,44 @@
       </c>
       <c r="DW33" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="DX33" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="DZ33" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EA33" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="DZ33" t="inlineStr"/>
+      <c r="EA33" t="inlineStr"/>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF33" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr"/>
@@ -16044,7 +16044,7 @@
         <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -16096,7 +16096,7 @@
         <v>4</v>
       </c>
       <c r="AD34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE34" t="n">
         <v>2.68</v>
@@ -16216,13 +16216,13 @@
         <v>3</v>
       </c>
       <c r="BR34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS34" t="n">
         <v>2</v>
       </c>
       <c r="BT34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU34" t="n">
         <v>1</v>
@@ -17337,16 +17337,8 @@
           <t>3.38</t>
         </is>
       </c>
-      <c r="DZ36" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EA36" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
+      <c r="DZ36" t="inlineStr"/>
+      <c r="EA36" t="inlineStr"/>
       <c r="EB36" t="inlineStr">
         <is>
           <t>1.35</t>
@@ -17392,16 +17384,8 @@
           <t>2.87</t>
         </is>
       </c>
-      <c r="EK36" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EL36" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
+      <c r="EK36" t="inlineStr"/>
+      <c r="EL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17467,13 +17451,13 @@
         <v>7</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T37" t="n">
         <v>11</v>
       </c>
       <c r="U37" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V37" t="n">
         <v>18</v>
@@ -17648,13 +17632,13 @@
         <v>103</v>
       </c>
       <c r="BZ37" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="CA37" t="n">
         <v>2.01</v>
       </c>
       <c r="CB37" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="CC37" t="n">
         <v>1</v>
@@ -17866,6 +17850,454 @@
       </c>
       <c r="EK37" t="inlineStr"/>
       <c r="EL37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>46079.91666666666</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>14</v>
+      </c>
+      <c r="U38" t="n">
+        <v>8</v>
+      </c>
+      <c r="V38" t="n">
+        <v>16</v>
+      </c>
+      <c r="W38" t="n">
+        <v>14</v>
+      </c>
+      <c r="X38" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Estádio Urbano Caldeira</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>611</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV38" t="n">
+        <v>45</v>
+      </c>
+      <c r="BW38" t="n">
+        <v>51</v>
+      </c>
+      <c r="BX38" t="n">
+        <v>89</v>
+      </c>
+      <c r="BY38" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CB38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR38" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS38" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU38" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV38" t="n">
+        <v>19</v>
+      </c>
+      <c r="CW38" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX38" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY38" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ38" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA38" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB38" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC38" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DI38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DJ38" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DM38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DN38" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DO38" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU38" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV38" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW38" t="inlineStr">
+        <is>
+          <t>3.53</t>
+        </is>
+      </c>
+      <c r="DX38" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="DY38" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="DZ38" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EA38" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB38" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC38" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="ED38" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EE38" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF38" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG38" t="inlineStr"/>
+      <c r="EH38" t="inlineStr"/>
+      <c r="EI38" t="inlineStr"/>
+      <c r="EJ38" t="inlineStr"/>
+      <c r="EK38" t="inlineStr"/>
+      <c r="EL38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -18036,7 +18036,7 @@
         <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>-1</v>
+        <v>8808</v>
       </c>
       <c r="BG38" t="n">
         <v>2</v>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL43" headerRowCount="1">
-  <autoFilter ref="A1:EL43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL47" headerRowCount="1">
+  <autoFilter ref="A1:EL47"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -280,12 +280,12 @@
     <tableColumn id="134" name="pinnacle_ft_over25"/>
     <tableColumn id="135" name="pinnacle_btts_yes"/>
     <tableColumn id="136" name="pinnacle_btts_no"/>
-    <tableColumn id="137" name="pinnacle_corners_over_85"/>
-    <tableColumn id="138" name="pinnacle_corners_under_85"/>
-    <tableColumn id="139" name="pinnacle_1st_half_over15"/>
-    <tableColumn id="140" name="pinnacle_1st_half_under15"/>
-    <tableColumn id="141" name="pinnacle_1st_half_over05"/>
-    <tableColumn id="142" name="pinnacle_1st_half_under05"/>
+    <tableColumn id="137" name="pinnacle_1st_half_over15"/>
+    <tableColumn id="138" name="pinnacle_1st_half_under15"/>
+    <tableColumn id="139" name="pinnacle_1st_half_over05"/>
+    <tableColumn id="140" name="pinnacle_1st_half_under05"/>
+    <tableColumn id="141" name="pinnacle_corners_over_85"/>
+    <tableColumn id="142" name="pinnacle_corners_under_85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL43"/>
+  <dimension ref="A1:EL47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -1410,32 +1410,32 @@
       </c>
       <c r="EG1" s="1" t="inlineStr">
         <is>
+          <t>pinnacle_1st_half_over15</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under15</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_over05</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>pinnacle_1st_half_under05</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
           <t>pinnacle_corners_over_85</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>pinnacle_corners_under_85</t>
-        </is>
-      </c>
-      <c r="EI1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over15</t>
-        </is>
-      </c>
-      <c r="EJ1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_under15</t>
-        </is>
-      </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_over05</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>pinnacle_1st_half_under05</t>
         </is>
       </c>
     </row>
@@ -1872,20 +1872,20 @@
           <t>1.85</t>
         </is>
       </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
       <c r="EI2" t="inlineStr"/>
       <c r="EJ2" t="inlineStr"/>
-      <c r="EK2" t="inlineStr"/>
-      <c r="EL2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2255,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP3" t="b">
         <v>1</v>
@@ -2768,28 +2768,28 @@
           <t>1.76</t>
         </is>
       </c>
-      <c r="EG4" t="inlineStr"/>
-      <c r="EH4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EK4" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EL4" t="inlineStr">
-        <is>
           <t>2.74</t>
         </is>
       </c>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3121,7 +3121,7 @@
         <v>1.67</v>
       </c>
       <c r="DE5" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
@@ -3224,20 +3224,20 @@
           <t>1.89</t>
         </is>
       </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
       <c r="EI5" t="inlineStr"/>
       <c r="EJ5" t="inlineStr"/>
-      <c r="EK5" t="inlineStr"/>
-      <c r="EL5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -3674,32 +3674,32 @@
       </c>
       <c r="EG6" t="inlineStr">
         <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="EH6" t="inlineStr">
+      <c r="EL6" t="inlineStr">
         <is>
           <t>2.56</t>
-        </is>
-      </c>
-      <c r="EI6" t="inlineStr">
-        <is>
-          <t>2.97</t>
-        </is>
-      </c>
-      <c r="EJ6" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EK6" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EL6" t="inlineStr">
-        <is>
-          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -3719,254 +3719,254 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>46050.95833333334</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
         <v>14</v>
       </c>
-      <c r="L7" t="n">
-        <v>15</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
+      <c r="X7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Estádio Urbano Caldeira</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD7" t="n">
         <v>5</v>
       </c>
-      <c r="S7" t="n">
-        <v>4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>20</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>25</v>
-      </c>
-      <c r="W7" t="n">
-        <v>10</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Arena Condá</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Rua Clevelândia, Bairro Centro, Chapecó, Santa Catarina</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3</v>
-      </c>
       <c r="AE7" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>3.31</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.5</v>
+        <v>3.32</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.53</v>
+        <v>2.73</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV7" t="n">
         <v>1</v>
       </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>626</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>13577</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>4</v>
       </c>
-      <c r="BA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>623</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>17551</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12</v>
-      </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL7" t="n">
         <v>2</v>
       </c>
       <c r="BM7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BN7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BS7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BT7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BU7" t="n">
         <v>1</v>
       </c>
       <c r="BV7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BW7" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="BX7" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BY7" t="n">
-        <v>151</v>
+        <v>87</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.84</v>
+        <v>1.5</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.13</v>
+        <v>2.76</v>
       </c>
       <c r="CC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG7" t="n">
         <v>0</v>
@@ -3990,89 +3990,89 @@
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CO7" t="n">
         <v>0</v>
       </c>
       <c r="CP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ7" t="n">
         <v>1</v>
       </c>
       <c r="CR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV7" t="n">
         <v>13</v>
       </c>
-      <c r="CS7" t="n">
-        <v>31</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU7" t="n">
+      <c r="CW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
         <v>4</v>
       </c>
-      <c r="CV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>18</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>3</v>
-      </c>
       <c r="DP7" t="b">
         <v>1</v>
       </c>
@@ -4083,77 +4083,69 @@
         <v>1</v>
       </c>
       <c r="DS7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV7" t="b">
         <v>1</v>
       </c>
       <c r="DW7" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="DY7" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="DZ7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EA7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EB7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EC7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="ED7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EE7" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EF7" t="inlineStr">
         <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EG7" t="inlineStr">
-        <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EH7" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
       <c r="EI7" t="inlineStr"/>
       <c r="EJ7" t="inlineStr"/>
       <c r="EK7" t="inlineStr"/>
@@ -4175,164 +4167,164 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
         <v>46050.95833333334</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>20</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W8" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="X8" t="n">
         <v>5</v>
       </c>
-      <c r="R8" t="n">
-        <v>6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V8" t="n">
-        <v>11</v>
-      </c>
-      <c r="W8" t="n">
-        <v>14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>14</v>
-      </c>
       <c r="Y8" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="Z8" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Estádio Urbano Caldeira</t>
+          <t>Arena Condá</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+          <t>Rua Clevelândia, Bairro Centro, Chapecó, Santa Catarina</t>
         </is>
       </c>
       <c r="AC8" t="n">
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>1</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
@@ -4344,7 +4336,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>13577</v>
+        <v>17551</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
@@ -4353,134 +4345,134 @@
         <v>1</v>
       </c>
       <c r="BI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>151</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>31</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU8" t="n">
         <v>4</v>
       </c>
-      <c r="BK8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR8" t="n">
+      <c r="CV8" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>18</v>
+      </c>
+      <c r="CY8" t="n">
         <v>4</v>
       </c>
-      <c r="BS8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>19</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>87</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CB8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>10</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>32</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW8" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ8" t="n">
         <v>0</v>
       </c>
@@ -4494,10 +4486,10 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DE8" t="n">
-        <v>3</v>
+        <v>0.33</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4539,73 +4531,81 @@
         <v>1</v>
       </c>
       <c r="DS8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV8" t="b">
         <v>1</v>
       </c>
       <c r="DW8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="DX8" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="DY8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="DZ8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EA8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EB8" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EC8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="ED8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EE8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EF8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="EG8" t="inlineStr"/>
       <c r="EH8" t="inlineStr"/>
       <c r="EI8" t="inlineStr"/>
       <c r="EJ8" t="inlineStr"/>
-      <c r="EK8" t="inlineStr"/>
-      <c r="EL8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5048,28 +5048,28 @@
           <t>1.64</t>
         </is>
       </c>
-      <c r="EG9" t="inlineStr"/>
-      <c r="EH9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EI9" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EJ9" t="inlineStr">
         <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EL9" t="inlineStr">
-        <is>
           <t>2.37</t>
         </is>
       </c>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5960,28 +5960,28 @@
           <t>1.83</t>
         </is>
       </c>
-      <c r="EG11" t="inlineStr"/>
-      <c r="EH11" t="inlineStr"/>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
       <c r="EI11" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EJ11" t="inlineStr">
         <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EK11" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EL11" t="inlineStr">
-        <is>
           <t>2.63</t>
         </is>
       </c>
+      <c r="EK11" t="inlineStr"/>
+      <c r="EL11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6416,28 +6416,28 @@
           <t>1.76</t>
         </is>
       </c>
-      <c r="EG12" t="inlineStr"/>
-      <c r="EH12" t="inlineStr"/>
+      <c r="EG12" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
       <c r="EI12" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EJ12" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EK12" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EL12" t="inlineStr">
-        <is>
           <t>3.27</t>
         </is>
       </c>
+      <c r="EK12" t="inlineStr"/>
+      <c r="EL12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6799,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -6872,28 +6872,28 @@
           <t>1.81</t>
         </is>
       </c>
-      <c r="EG13" t="inlineStr"/>
-      <c r="EH13" t="inlineStr"/>
+      <c r="EG13" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EI13" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EJ13" t="inlineStr">
         <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EK13" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EL13" t="inlineStr">
-        <is>
           <t>2.71</t>
         </is>
       </c>
+      <c r="EK13" t="inlineStr"/>
+      <c r="EL13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7336,28 +7336,28 @@
           <t>1.82</t>
         </is>
       </c>
-      <c r="EG14" t="inlineStr"/>
-      <c r="EH14" t="inlineStr"/>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EI14" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EJ14" t="inlineStr">
         <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EK14" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EL14" t="inlineStr">
-        <is>
           <t>2.68</t>
         </is>
       </c>
+      <c r="EK14" t="inlineStr"/>
+      <c r="EL14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7694,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DE15" t="n">
         <v>1</v>
@@ -7800,28 +7800,28 @@
           <t>1.92</t>
         </is>
       </c>
-      <c r="EG15" t="inlineStr"/>
-      <c r="EH15" t="inlineStr"/>
+      <c r="EG15" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EI15" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EJ15" t="inlineStr">
         <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EK15" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EL15" t="inlineStr">
-        <is>
           <t>2.78</t>
         </is>
       </c>
+      <c r="EK15" t="inlineStr"/>
+      <c r="EL15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8158,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
@@ -8256,28 +8256,28 @@
           <t>1.99</t>
         </is>
       </c>
-      <c r="EG16" t="inlineStr"/>
-      <c r="EH16" t="inlineStr"/>
+      <c r="EG16" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
       <c r="EI16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EK16" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EL16" t="inlineStr">
-        <is>
           <t>2.86</t>
         </is>
       </c>
+      <c r="EK16" t="inlineStr"/>
+      <c r="EL16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8720,20 +8720,20 @@
           <t>1.69</t>
         </is>
       </c>
-      <c r="EG17" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EH17" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
+      <c r="EG17" t="inlineStr"/>
+      <c r="EH17" t="inlineStr"/>
       <c r="EI17" t="inlineStr"/>
       <c r="EJ17" t="inlineStr"/>
-      <c r="EK17" t="inlineStr"/>
-      <c r="EL17" t="inlineStr"/>
+      <c r="EK17" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9073,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -9178,32 +9178,32 @@
       </c>
       <c r="EG18" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EJ18" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr">
+        <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="EH18" t="inlineStr">
+      <c r="EL18" t="inlineStr">
         <is>
           <t>2.36</t>
-        </is>
-      </c>
-      <c r="EI18" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="EJ18" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EK18" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EL18" t="inlineStr">
-        <is>
-          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -9542,11 +9542,11 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE19" t="n">
         <v>0.5</v>
       </c>
-      <c r="DE19" t="n">
-        <v>1</v>
-      </c>
       <c r="DF19" t="n">
         <v>0</v>
       </c>
@@ -9575,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -10524,20 +10524,20 @@
           <t>1.79</t>
         </is>
       </c>
-      <c r="EG21" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EH21" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="EG21" t="inlineStr"/>
+      <c r="EH21" t="inlineStr"/>
       <c r="EI21" t="inlineStr"/>
       <c r="EJ21" t="inlineStr"/>
-      <c r="EK21" t="inlineStr"/>
-      <c r="EL21" t="inlineStr"/>
+      <c r="EK21" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10982,32 +10982,32 @@
       </c>
       <c r="EG22" t="inlineStr">
         <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EH22" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EI22" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EJ22" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="EK22" t="inlineStr">
+        <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="EH22" t="inlineStr">
+      <c r="EL22" t="inlineStr">
         <is>
           <t>2.38</t>
-        </is>
-      </c>
-      <c r="EI22" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
-      <c r="EJ22" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EK22" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EL22" t="inlineStr">
-        <is>
-          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -11379,7 +11379,7 @@
         <v>1.86</v>
       </c>
       <c r="DO23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -11452,28 +11452,28 @@
           <t>1.97</t>
         </is>
       </c>
-      <c r="EG23" t="inlineStr"/>
-      <c r="EH23" t="inlineStr"/>
+      <c r="EG23" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EJ23" t="inlineStr">
         <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EK23" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EL23" t="inlineStr">
-        <is>
           <t>2.80</t>
         </is>
       </c>
+      <c r="EK23" t="inlineStr"/>
+      <c r="EL23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11835,7 +11835,7 @@
         <v>2.47</v>
       </c>
       <c r="DO24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11908,28 +11908,28 @@
           <t>1.82</t>
         </is>
       </c>
-      <c r="EG24" t="inlineStr"/>
-      <c r="EH24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr">
+        <is>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EH24" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
       <c r="EI24" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EJ24" t="inlineStr">
         <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK24" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EL24" t="inlineStr">
-        <is>
           <t>3.22</t>
         </is>
       </c>
+      <c r="EK24" t="inlineStr"/>
+      <c r="EL24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12299,7 +12299,7 @@
         <v>2.3</v>
       </c>
       <c r="DO25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -12372,20 +12372,20 @@
           <t>1.93</t>
         </is>
       </c>
-      <c r="EG25" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EH25" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
+      <c r="EG25" t="inlineStr"/>
+      <c r="EH25" t="inlineStr"/>
       <c r="EI25" t="inlineStr"/>
       <c r="EJ25" t="inlineStr"/>
-      <c r="EK25" t="inlineStr"/>
-      <c r="EL25" t="inlineStr"/>
+      <c r="EK25" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EL25" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12722,7 +12722,7 @@
         <v>50</v>
       </c>
       <c r="DD26" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DE26" t="n">
         <v>3</v>
@@ -12830,32 +12830,32 @@
       </c>
       <c r="EG26" t="inlineStr">
         <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EH26" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI26" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EJ26" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EK26" t="inlineStr">
+        <is>
           <t>1.68</t>
         </is>
       </c>
-      <c r="EH26" t="inlineStr">
+      <c r="EL26" t="inlineStr">
         <is>
           <t>2.13</t>
-        </is>
-      </c>
-      <c r="EI26" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="EJ26" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EK26" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EL26" t="inlineStr">
-        <is>
-          <t>3.18</t>
         </is>
       </c>
     </row>
@@ -13292,28 +13292,28 @@
           <t>1.90</t>
         </is>
       </c>
-      <c r="EG27" t="inlineStr"/>
-      <c r="EH27" t="inlineStr"/>
+      <c r="EG27" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EH27" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
       <c r="EI27" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EJ27" t="inlineStr">
         <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EK27" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EL27" t="inlineStr">
-        <is>
           <t>2.76</t>
         </is>
       </c>
+      <c r="EK27" t="inlineStr"/>
+      <c r="EL27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13748,20 +13748,20 @@
           <t>1.76</t>
         </is>
       </c>
-      <c r="EG28" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EH28" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
+      <c r="EG28" t="inlineStr"/>
+      <c r="EH28" t="inlineStr"/>
       <c r="EI28" t="inlineStr"/>
       <c r="EJ28" t="inlineStr"/>
-      <c r="EK28" t="inlineStr"/>
-      <c r="EL28" t="inlineStr"/>
+      <c r="EK28" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EL28" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14101,7 +14101,7 @@
         <v>1</v>
       </c>
       <c r="DE29" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF29" t="n">
         <v>0</v>
@@ -14131,7 +14131,7 @@
         <v>4.58</v>
       </c>
       <c r="DO29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14541,7 +14541,7 @@
         <v>0</v>
       </c>
       <c r="DE30" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DF30" t="n">
         <v>0</v>
@@ -14571,7 +14571,7 @@
         <v>3.67</v>
       </c>
       <c r="DO30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -15086,32 +15086,32 @@
       </c>
       <c r="EG31" t="inlineStr">
         <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EH31" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EI31" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EJ31" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EK31" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="EH31" t="inlineStr">
+      <c r="EL31" t="inlineStr">
         <is>
           <t>2.50</t>
-        </is>
-      </c>
-      <c r="EI31" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EJ31" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EK31" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EL31" t="inlineStr">
-        <is>
-          <t>2.63</t>
         </is>
       </c>
     </row>
@@ -15882,7 +15882,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="DE33" t="n">
         <v>0.67</v>
@@ -15915,7 +15915,7 @@
         <v>2.76</v>
       </c>
       <c r="DO33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16363,7 +16363,7 @@
         <v>1.6</v>
       </c>
       <c r="DO34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16438,32 +16438,32 @@
       </c>
       <c r="EG34" t="inlineStr">
         <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
           <t>1.55</t>
         </is>
       </c>
-      <c r="EH34" t="inlineStr">
+      <c r="EL34" t="inlineStr">
         <is>
           <t>2.33</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>3.46</t>
-        </is>
-      </c>
-      <c r="EJ34" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EK34" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EL34" t="inlineStr">
-        <is>
-          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -16908,28 +16908,28 @@
           <t>1.79</t>
         </is>
       </c>
-      <c r="EG35" t="inlineStr"/>
-      <c r="EH35" t="inlineStr"/>
+      <c r="EG35" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EH35" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
       <c r="EI35" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EJ35" t="inlineStr">
         <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EK35" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EL35" t="inlineStr">
-        <is>
           <t>2.85</t>
         </is>
       </c>
+      <c r="EK35" t="inlineStr"/>
+      <c r="EL35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -17269,7 +17269,7 @@
         <v>3</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF36" t="n">
         <v>3</v>
@@ -17299,7 +17299,7 @@
         <v>3.37</v>
       </c>
       <c r="DO36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -17372,28 +17372,28 @@
           <t>1.97</t>
         </is>
       </c>
-      <c r="EG36" t="inlineStr"/>
-      <c r="EH36" t="inlineStr"/>
+      <c r="EG36" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EH36" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
       <c r="EI36" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EJ36" t="inlineStr">
         <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EK36" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="EL36" t="inlineStr">
-        <is>
           <t>3.14</t>
         </is>
       </c>
+      <c r="EK36" t="inlineStr"/>
+      <c r="EL36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17730,7 +17730,7 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="DE37" t="n">
         <v>0</v>
@@ -17763,7 +17763,7 @@
         <v>2.85</v>
       </c>
       <c r="DO37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -17828,28 +17828,28 @@
           <t>2.03</t>
         </is>
       </c>
-      <c r="EG37" t="inlineStr"/>
-      <c r="EH37" t="inlineStr"/>
+      <c r="EG37" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
       <c r="EI37" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EJ37" t="inlineStr">
         <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EK37" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EL37" t="inlineStr">
-        <is>
           <t>2.87</t>
         </is>
       </c>
+      <c r="EK37" t="inlineStr"/>
+      <c r="EL37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18219,7 +18219,7 @@
         <v>2.39</v>
       </c>
       <c r="DO38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18375,7 +18375,7 @@
         <v>16</v>
       </c>
       <c r="W39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39" t="n">
         <v>8</v>
@@ -18814,7 +18814,7 @@
         <v>15</v>
       </c>
       <c r="X40" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="n">
         <v>35</v>
@@ -19120,82 +19120,82 @@
       </c>
       <c r="DW40" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="DX40" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="DZ40" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EA40" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EB40" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="EC40" t="inlineStr">
+        <is>
           <t>3.25</t>
         </is>
       </c>
-      <c r="DZ40" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EA40" t="inlineStr">
+      <c r="ED40" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="EB40" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="EC40" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="ED40" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EF40" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EI40" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>2.56</t>
         </is>
       </c>
     </row>
@@ -19592,22 +19592,22 @@
       </c>
       <c r="DW41" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="DX41" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="DY41" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="DZ41" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EA41" t="inlineStr">
@@ -19622,52 +19622,52 @@
       </c>
       <c r="EC41" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="ED41" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EE41" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="EF41" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG41" t="inlineStr">
         <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EH41" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI41" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ41" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EK41" t="inlineStr">
+        <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="EH41" t="inlineStr">
+      <c r="EL41" t="inlineStr">
         <is>
           <t>2.44</t>
-        </is>
-      </c>
-      <c r="EI41" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="EJ41" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EK41" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="EL41" t="inlineStr">
-        <is>
-          <t>3.02</t>
         </is>
       </c>
     </row>
@@ -19979,7 +19979,7 @@
         <v>1</v>
       </c>
       <c r="CU42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CV42" t="n">
         <v>15</v>
@@ -20064,76 +20064,68 @@
       </c>
       <c r="DW42" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="DX42" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="DY42" t="inlineStr">
         <is>
-          <t>6.28</t>
-        </is>
-      </c>
-      <c r="DZ42" t="inlineStr">
+          <t>5.82</t>
+        </is>
+      </c>
+      <c r="DZ42" t="inlineStr"/>
+      <c r="EA42" t="inlineStr"/>
+      <c r="EB42" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC42" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="ED42" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EE42" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EF42" t="inlineStr">
         <is>
           <t>1.70</t>
         </is>
       </c>
-      <c r="EA42" t="inlineStr">
-        <is>
-          <t>2.07</t>
-        </is>
-      </c>
-      <c r="EB42" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="EC42" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="ED42" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EE42" t="inlineStr">
-        <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="EF42" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EG42" t="inlineStr"/>
-      <c r="EH42" t="inlineStr"/>
+      <c r="EG42" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EH42" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EI42" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EJ42" t="inlineStr">
         <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EK42" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EL42" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EK42" t="inlineStr"/>
+      <c r="EL42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -20520,68 +20512,1908 @@
       </c>
       <c r="DW43" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="DX43" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="DY43" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="DZ43" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EA43" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EB43" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC43" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="ED43" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EE43" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EF43" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EG43" t="inlineStr">
+        <is>
+          <t>2.97</t>
+        </is>
+      </c>
+      <c r="EH43" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI43" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EJ43" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
+      <c r="EK43" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EL43" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>46093.91666666666</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>10</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7</v>
+      </c>
+      <c r="S44" t="n">
+        <v>7</v>
+      </c>
+      <c r="T44" t="n">
+        <v>8</v>
+      </c>
+      <c r="U44" t="n">
+        <v>10</v>
+      </c>
+      <c r="V44" t="n">
+        <v>15</v>
+      </c>
+      <c r="W44" t="n">
+        <v>7</v>
+      </c>
+      <c r="X44" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
+        </is>
+      </c>
+      <c r="AC44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>617</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU44" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV44" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW44" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX44" t="n">
+        <v>83</v>
+      </c>
+      <c r="BY44" t="n">
+        <v>121</v>
+      </c>
+      <c r="BZ44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA44" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CB44" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR44" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS44" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU44" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV44" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW44" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX44" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY44" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ44" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA44" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB44" t="n">
+        <v>75</v>
+      </c>
+      <c r="DC44" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD44" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF44" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH44" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DI44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ44" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="DM44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DN44" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DO44" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP44" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ44" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV44" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW44" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="DX44" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="DY44" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="DZ44" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="EA44" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EB44" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="EC44" t="inlineStr">
+        <is>
+          <t>3.48</t>
+        </is>
+      </c>
+      <c r="ED44" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EB43" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EC43" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="ED43" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EE43" t="inlineStr">
+      <c r="EE44" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EF44" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EG44" t="inlineStr"/>
+      <c r="EH44" t="inlineStr"/>
+      <c r="EI44" t="inlineStr"/>
+      <c r="EJ44" t="inlineStr"/>
+      <c r="EK44" t="inlineStr"/>
+      <c r="EL44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>46093.9375</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5</v>
+      </c>
+      <c r="L45" t="n">
+        <v>14</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>11</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>17</v>
+      </c>
+      <c r="V45" t="n">
+        <v>8</v>
+      </c>
+      <c r="W45" t="n">
+        <v>6</v>
+      </c>
+      <c r="X45" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Estádio Club de Regatas Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Rua Gal Almério de Moura 131, Bairro Vasco da Gama, Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AC45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>625</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU45" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV45" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW45" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX45" t="n">
+        <v>128</v>
+      </c>
+      <c r="BY45" t="n">
+        <v>81</v>
+      </c>
+      <c r="BZ45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CA45" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM45" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR45" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS45" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU45" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV45" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW45" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX45" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY45" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ45" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA45" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB45" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC45" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG45" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DI45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DJ45" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK45" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL45" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DM45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DN45" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="DO45" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP45" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ45" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR45" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU45" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV45" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW45" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="DX45" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="DY45" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="DZ45" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EA45" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="EB45" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EC45" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="ED45" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EE45" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EF45" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EG45" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="EH45" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EI45" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EJ45" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="EK45" t="inlineStr"/>
+      <c r="EL45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>46093.95833333334</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>11</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6</v>
+      </c>
+      <c r="L46" t="n">
+        <v>17</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>7</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>11</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
+        <v>18</v>
+      </c>
+      <c r="V46" t="n">
+        <v>7</v>
+      </c>
+      <c r="W46" t="n">
+        <v>13</v>
+      </c>
+      <c r="X46" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Morumbí</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Praca Roberto Gomes Pedrosa 1, Morumbi, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>618</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI46" t="n">
+        <v>6</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV46" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW46" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX46" t="n">
+        <v>105</v>
+      </c>
+      <c r="BY46" t="n">
+        <v>68</v>
+      </c>
+      <c r="BZ46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CA46" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR46" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS46" t="n">
+        <v>32</v>
+      </c>
+      <c r="CT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU46" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV46" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW46" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX46" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY46" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ46" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA46" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC46" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD46" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF46" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DJ46" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DM46" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DN46" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DO46" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP46" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ46" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR46" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS46" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT46" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU46" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV46" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW46" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="DX46" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="DY46" t="inlineStr">
+        <is>
+          <t>8.92</t>
+        </is>
+      </c>
+      <c r="DZ46" t="inlineStr"/>
+      <c r="EA46" t="inlineStr"/>
+      <c r="EB46" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr">
+        <is>
+          <t>2.89</t>
+        </is>
+      </c>
+      <c r="ED46" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EF46" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EG46" t="inlineStr"/>
+      <c r="EH46" t="inlineStr"/>
+      <c r="EI46" t="inlineStr"/>
+      <c r="EJ46" t="inlineStr"/>
+      <c r="EK46" t="inlineStr"/>
+      <c r="EL46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>46094.02083333334</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>10</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>6</v>
+      </c>
+      <c r="R47" t="n">
+        <v>8</v>
+      </c>
+      <c r="S47" t="n">
+        <v>7</v>
+      </c>
+      <c r="T47" t="n">
+        <v>12</v>
+      </c>
+      <c r="U47" t="n">
+        <v>13</v>
+      </c>
+      <c r="V47" t="n">
+        <v>20</v>
+      </c>
+      <c r="W47" t="n">
+        <v>11</v>
+      </c>
+      <c r="X47" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>61</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Arena do Grêmio</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>19472</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV47" t="n">
+        <v>27</v>
+      </c>
+      <c r="BW47" t="n">
+        <v>48</v>
+      </c>
+      <c r="BX47" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY47" t="n">
+        <v>121</v>
+      </c>
+      <c r="BZ47" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CA47" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CB47" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="CC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR47" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS47" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU47" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV47" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW47" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX47" t="n">
+        <v>13</v>
+      </c>
+      <c r="CY47" t="n">
+        <v>5</v>
+      </c>
+      <c r="CZ47" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA47" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB47" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC47" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD47" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DE47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF47" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ47" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK47" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="DM47" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DN47" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="DO47" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP47" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ47" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU47" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV47" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW47" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="DX47" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="DY47" t="inlineStr">
+        <is>
+          <t>3.31</t>
+        </is>
+      </c>
+      <c r="DZ47" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EA47" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB47" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="ED47" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EF47" t="inlineStr">
         <is>
           <t>2.03</t>
         </is>
       </c>
-      <c r="EF43" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="EG43" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EH43" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="EI43" t="inlineStr"/>
-      <c r="EJ43" t="inlineStr"/>
-      <c r="EK43" t="inlineStr"/>
-      <c r="EL43" t="inlineStr"/>
+      <c r="EG47" t="inlineStr">
+        <is>
+          <t>3.11</t>
+        </is>
+      </c>
+      <c r="EH47" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EI47" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="EJ47" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="EK47" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EL47" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL47" headerRowCount="1">
-  <autoFilter ref="A1:EL47"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL56" headerRowCount="1">
+  <autoFilter ref="A1:EL56"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL47"/>
+  <dimension ref="A1:EL56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -1903,143 +1903,143 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
         <v>46050.91666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
         <v>5</v>
       </c>
-      <c r="L3" t="n">
-        <v>6</v>
-      </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
+        <v>13</v>
+      </c>
+      <c r="U3" t="n">
         <v>20</v>
       </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
       <c r="V3" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="W3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="Z3" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Estádio Major Antônio Couto Pereira</t>
+          <t>Estádio Manoel Barradas</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
+          <t>Rua Artêmio Castro Valente 1, Bairro Nossa Senhora da Vitória, Salvador, Bahia</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI3" t="n">
         <v>2.21</v>
       </c>
-      <c r="AF3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>4.8</v>
+        <v>3.82</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AL3" t="n">
         <v>1.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AO3" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -2048,19 +2048,19 @@
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>635</v>
+        <v>610</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>19535</v>
+        <v>16511</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
@@ -2081,22 +2081,22 @@
         <v>1</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
         <v>2</v>
       </c>
       <c r="BN3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO3" t="n">
         <v>2</v>
@@ -2108,106 +2108,106 @@
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BS3" t="n">
         <v>4</v>
       </c>
       <c r="BT3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU3" t="n">
         <v>1</v>
       </c>
       <c r="BV3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>81</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU3" t="n">
         <v>17</v>
       </c>
-      <c r="BW3" t="n">
-        <v>69</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>74</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>127</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>10</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>24</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>19</v>
-      </c>
       <c r="CV3" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX3" t="n">
         <v>9</v>
       </c>
-      <c r="CW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>15</v>
-      </c>
       <c r="CY3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CZ3" t="n">
         <v>0</v>
@@ -2222,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="DQ3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR3" t="b">
         <v>0</v>
@@ -2280,58 +2280,66 @@
       </c>
       <c r="DW3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="DX3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="DY3" t="inlineStr">
         <is>
-          <t>2.89</t>
-        </is>
-      </c>
-      <c r="DZ3" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
       <c r="EB3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="EC3" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="ED3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EE3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="EF3" t="inlineStr">
         <is>
-          <t>1.74</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr"/>
-      <c r="EH3" t="inlineStr"/>
-      <c r="EI3" t="inlineStr"/>
-      <c r="EJ3" t="inlineStr"/>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
       <c r="EK3" t="inlineStr"/>
       <c r="EL3" t="inlineStr"/>
     </row>
@@ -2351,12 +2359,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -2366,25 +2374,25 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2393,59 +2401,51 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="n">
         <v>7</v>
       </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
+        <v>14</v>
+      </c>
+      <c r="V4" t="n">
         <v>13</v>
       </c>
-      <c r="T4" t="n">
-        <v>13</v>
-      </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X4" t="n">
         <v>20</v>
       </c>
-      <c r="V4" t="n">
-        <v>14</v>
-      </c>
-      <c r="W4" t="n">
-        <v>13</v>
-      </c>
-      <c r="X4" t="n">
-        <v>17</v>
-      </c>
       <c r="Y4" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="Z4" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Estádio Manoel Barradas</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Rua Artêmio Castro Valente 1, Bairro Nossa Senhora da Vitória, Salvador, Bahia</t>
-        </is>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.64</v>
+        <v>2.34</v>
       </c>
       <c r="AH4" t="n">
         <v>1.36</v>
@@ -2454,61 +2454,61 @@
         <v>2.21</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.9</v>
+        <v>3.37</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ4" t="n">
         <v>2</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB4" t="n">
-        <v>610</v>
+        <v>-1</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>16511</v>
+        <v>25770</v>
       </c>
       <c r="BG4" t="n">
         <v>2</v>
@@ -2532,61 +2532,61 @@
         <v>1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BM4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="BO4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BR4" t="n">
         <v>2</v>
       </c>
       <c r="BS4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU4" t="n">
         <v>1</v>
       </c>
       <c r="BV4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BW4" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BX4" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="BY4" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.99</v>
+        <v>1.3</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.16</v>
+        <v>2.87</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2634,28 +2634,28 @@
         <v>1</v>
       </c>
       <c r="CR4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CS4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CT4" t="n">
         <v>1</v>
       </c>
       <c r="CU4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CV4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CW4" t="n">
         <v>1</v>
       </c>
       <c r="CX4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CY4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ4" t="n">
         <v>0</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DP4" t="b">
         <v>1</v>
@@ -2712,10 +2712,10 @@
         <v>1</v>
       </c>
       <c r="DR4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT4" t="b">
         <v>0</v>
@@ -2724,25 +2724,33 @@
         <v>0</v>
       </c>
       <c r="DV4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="DZ4" t="inlineStr"/>
-      <c r="EA4" t="inlineStr"/>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="EB4" t="inlineStr">
         <is>
           <t>1.41</t>
@@ -2750,46 +2758,38 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EG4" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="EH4" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EI4" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EJ4" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="EK4" t="inlineStr"/>
-      <c r="EL4" t="inlineStr"/>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2807,43 +2807,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
         <v>46050.91666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
-        <v>7</v>
-      </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2852,258 +2852,266 @@
         <v>2</v>
       </c>
       <c r="R5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" t="n">
         <v>6</v>
       </c>
-      <c r="S5" t="n">
-        <v>12</v>
-      </c>
       <c r="T5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="U5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="W5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Estádio Major Antônio Couto Pereira</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
+        </is>
+      </c>
       <c r="AC5" t="n">
         <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.2</v>
+        <v>2.21</v>
       </c>
       <c r="AF5" t="n">
         <v>3.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.36</v>
       </c>
-      <c r="AI5" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AP5" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.56</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>635</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>19535</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN5" t="n">
         <v>4</v>
       </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>25770</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
         <v>4</v>
       </c>
-      <c r="BL5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN5" t="n">
+      <c r="BS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>17</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>69</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>74</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>127</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV5" t="n">
         <v>9</v>
       </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>97</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>63</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>10</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>20</v>
-      </c>
-      <c r="CV5" t="n">
-        <v>14</v>
-      </c>
       <c r="CW5" t="n">
         <v>1</v>
       </c>
       <c r="CX5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="CY5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="CZ5" t="n">
         <v>0</v>
@@ -3118,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="DE5" t="n">
         <v>1.33</v>
@@ -3151,19 +3159,19 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP5" t="b">
         <v>1</v>
       </c>
       <c r="DQ5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="b">
         <v>0</v>
@@ -3172,72 +3180,64 @@
         <v>0</v>
       </c>
       <c r="DV5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr"/>
       <c r="EH5" t="inlineStr"/>
       <c r="EI5" t="inlineStr"/>
       <c r="EJ5" t="inlineStr"/>
-      <c r="EK5" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4945,7 +4945,7 @@
         <v>3</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DF9" t="n">
         <v>0</v>
@@ -4975,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5409,7 +5409,7 @@
         <v>1.67</v>
       </c>
       <c r="DE10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DF10" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DE11" t="n">
         <v>0.33</v>
@@ -5887,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -6343,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP12" t="b">
         <v>1</v>
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6799,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP13" t="b">
         <v>1</v>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE14" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -7697,7 +7697,7 @@
         <v>0.67</v>
       </c>
       <c r="DE15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DF15" t="n">
         <v>0</v>
@@ -7727,7 +7727,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -7854,25 +7854,25 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -7887,251 +7887,251 @@
         <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
         <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V16" t="n">
         <v>9</v>
       </c>
       <c r="W16" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="Z16" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Arena do Grêmio</t>
+          <t>Allianz Parque</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
+          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.18</v>
+        <v>4.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.82</v>
+        <v>7.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AL16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>619</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>8953</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>1.91</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>616</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>29</v>
-      </c>
-      <c r="BW16" t="n">
+      <c r="CA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR16" t="n">
         <v>17</v>
       </c>
-      <c r="BX16" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>77</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>2</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>9</v>
-      </c>
       <c r="CS16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="CT16" t="n">
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CV16" t="n">
         <v>13</v>
@@ -8140,10 +8140,10 @@
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CY16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
@@ -8158,10 +8158,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DI16" t="n">
         <v>3</v>
@@ -8191,7 +8191,7 @@
         <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="DP16" t="b">
         <v>1</v>
@@ -8216,68 +8216,68 @@
       </c>
       <c r="DW16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="DZ16" t="inlineStr"/>
-      <c r="EA16" t="inlineStr"/>
+          <t>10.32</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EF16" t="inlineStr">
         <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="EG16" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="EH16" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr"/>
+      <c r="EJ16" t="inlineStr"/>
+      <c r="EK16" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="EJ16" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EK16" t="inlineStr"/>
-      <c r="EL16" t="inlineStr"/>
+      <c r="EL16" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -8310,25 +8310,25 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
         <v>6</v>
       </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>10</v>
-      </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -8343,116 +8343,116 @@
         <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
         <v>5</v>
       </c>
       <c r="U17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="V17" t="n">
         <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="Z17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Allianz Parque</t>
+          <t>Arena do Grêmio</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
+          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
         </is>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX17" t="n">
         <v>4</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2</v>
-      </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA17" t="n">
         <v>3</v>
       </c>
       <c r="BB17" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>8953</v>
+        <v>-1</v>
       </c>
       <c r="BG17" t="n">
         <v>2</v>
@@ -8473,25 +8473,25 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL17" t="n">
         <v>2</v>
       </c>
       <c r="BM17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BN17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
         <v>1</v>
@@ -8500,46 +8500,46 @@
         <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BW17" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="BX17" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="BY17" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
       <c r="CM17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CN17" t="n">
         <v>0</v>
@@ -8572,22 +8572,22 @@
         <v>0</v>
       </c>
       <c r="CP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ17" t="n">
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="CS17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="CT17" t="n">
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV17" t="n">
         <v>13</v>
@@ -8596,10 +8596,10 @@
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CY17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
@@ -8614,10 +8614,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI17" t="n">
         <v>3</v>
@@ -8672,68 +8672,68 @@
       </c>
       <c r="DW17" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>10.32</t>
-        </is>
-      </c>
-      <c r="DZ17" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EA17" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="DZ17" t="inlineStr"/>
+      <c r="EA17" t="inlineStr"/>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EF17" t="inlineStr">
         <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EG17" t="inlineStr"/>
-      <c r="EH17" t="inlineStr"/>
-      <c r="EI17" t="inlineStr"/>
-      <c r="EJ17" t="inlineStr"/>
-      <c r="EK17" t="inlineStr">
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
         <is>
           <t>1.45</t>
         </is>
       </c>
-      <c r="EL17" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr"/>
+      <c r="EL17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9103,7 +9103,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -9982,7 +9982,7 @@
         <v>0</v>
       </c>
       <c r="DD20" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DE20" t="n">
         <v>2.33</v>
@@ -10015,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -10418,10 +10418,10 @@
         <v>0</v>
       </c>
       <c r="DD21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10451,7 +10451,7 @@
         <v>3.73</v>
       </c>
       <c r="DO21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -10907,7 +10907,7 @@
         <v>2.93</v>
       </c>
       <c r="DO22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP22" t="b">
         <v>1</v>
@@ -11805,7 +11805,7 @@
         <v>1.67</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="DF24" t="n">
         <v>1</v>
@@ -11835,7 +11835,7 @@
         <v>2.47</v>
       </c>
       <c r="DO24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -11947,164 +11947,164 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>46065.02083333334</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>26</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Estádio Club de Regatas Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Rua Gal Almério de Moura 131, Bairro Vasco da Gama, Rio de Janeiro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
         <v>4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>18</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>7</v>
-      </c>
-      <c r="X25" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Morumbí</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Praca Roberto Gomes Pedrosa 1, Morumbi, São Paulo</t>
-        </is>
-      </c>
-      <c r="AC25" t="n">
-        <v>3</v>
       </c>
       <c r="AD25" t="n">
         <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AF25" t="n">
         <v>3.2</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AO25" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.53</v>
+        <v>2.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AU25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
         <v>1</v>
       </c>
       <c r="BB25" t="n">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="BC25" t="n">
         <v>0</v>
@@ -12116,7 +12116,7 @@
         <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>18491</v>
+        <v>-1</v>
       </c>
       <c r="BG25" t="n">
         <v>2</v>
@@ -12125,73 +12125,73 @@
         <v>1</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BK25" t="n">
         <v>3</v>
       </c>
       <c r="BL25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BN25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BO25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP25" t="n">
         <v>2</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BR25" t="n">
         <v>2</v>
       </c>
       <c r="BS25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BT25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU25" t="n">
         <v>1</v>
       </c>
       <c r="BV25" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="BW25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BX25" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="BY25" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="BZ25" t="n">
-        <v>1.86</v>
+        <v>2.49</v>
       </c>
       <c r="CA25" t="n">
-        <v>0.61</v>
+        <v>0.93</v>
       </c>
       <c r="CB25" t="n">
-        <v>2.47</v>
+        <v>3.41</v>
       </c>
       <c r="CC25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD25" t="n">
         <v>0</v>
       </c>
       <c r="CE25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF25" t="n">
         <v>0</v>
@@ -12218,7 +12218,7 @@
         <v>0</v>
       </c>
       <c r="CN25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO25" t="n">
         <v>0</v>
@@ -12230,10 +12230,10 @@
         <v>1</v>
       </c>
       <c r="CR25" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="CS25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CT25" t="n">
         <v>1</v>
@@ -12242,61 +12242,61 @@
         <v>14</v>
       </c>
       <c r="CV25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CW25" t="n">
         <v>1</v>
       </c>
       <c r="CX25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="CY25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CZ25" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA25" t="n">
         <v>100</v>
       </c>
       <c r="DB25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="DE25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DF25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DG25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH25" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="DI25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DJ25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK25" t="n">
         <v>0</v>
       </c>
       <c r="DL25" t="n">
-        <v>1.09</v>
+        <v>3.13</v>
       </c>
       <c r="DM25" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="DN25" t="n">
-        <v>2.3</v>
+        <v>4.39</v>
       </c>
       <c r="DO25" t="n">
         <v>5</v>
@@ -12305,7 +12305,7 @@
         <v>1</v>
       </c>
       <c r="DQ25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR25" t="b">
         <v>0</v>
@@ -12324,22 +12324,22 @@
       </c>
       <c r="DW25" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="DX25" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="DY25" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="DZ25" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EA25" t="inlineStr">
@@ -12349,41 +12349,57 @@
       </c>
       <c r="EB25" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EC25" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="ED25" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EE25" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EF25" t="inlineStr">
         <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EG25" t="inlineStr"/>
-      <c r="EH25" t="inlineStr"/>
-      <c r="EI25" t="inlineStr"/>
-      <c r="EJ25" t="inlineStr"/>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EG25" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="EH25" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EI25" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EJ25" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
       <c r="EK25" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EL25" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.13</t>
         </is>
       </c>
     </row>
@@ -12403,164 +12419,164 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>46065.02083333334</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>18</v>
+      </c>
+      <c r="V26" t="n">
         <v>5</v>
       </c>
-      <c r="U26" t="n">
-        <v>26</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8</v>
-      </c>
       <c r="W26" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="Z26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Estádio Club de Regatas Vasco da Gama</t>
+          <t>Morumbí</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Rua Gal Almério de Moura 131, Bairro Vasco da Gama, Rio de Janeiro, Rio de Janeiro</t>
+          <t>Praca Roberto Gomes Pedrosa 1, Morumbi, São Paulo</t>
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD26" t="n">
         <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AF26" t="n">
         <v>3.2</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AO26" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.85</v>
+        <v>2.53</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AU26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA26" t="n">
         <v>1</v>
       </c>
       <c r="BB26" t="n">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="BC26" t="n">
         <v>0</v>
@@ -12572,7 +12588,7 @@
         <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>-1</v>
+        <v>18491</v>
       </c>
       <c r="BG26" t="n">
         <v>2</v>
@@ -12581,73 +12597,73 @@
         <v>1</v>
       </c>
       <c r="BI26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BJ26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN26" t="n">
         <v>4</v>
       </c>
-      <c r="BK26" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>3</v>
-      </c>
       <c r="BO26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP26" t="n">
         <v>2</v>
       </c>
       <c r="BQ26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR26" t="n">
         <v>2</v>
       </c>
       <c r="BS26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
       </c>
       <c r="BV26" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="BW26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BX26" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="BY26" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="BZ26" t="n">
-        <v>2.49</v>
+        <v>1.86</v>
       </c>
       <c r="CA26" t="n">
-        <v>0.93</v>
+        <v>0.61</v>
       </c>
       <c r="CB26" t="n">
-        <v>3.41</v>
+        <v>2.47</v>
       </c>
       <c r="CC26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD26" t="n">
         <v>0</v>
       </c>
       <c r="CE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF26" t="n">
         <v>0</v>
@@ -12674,7 +12690,7 @@
         <v>0</v>
       </c>
       <c r="CN26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO26" t="n">
         <v>0</v>
@@ -12686,10 +12702,10 @@
         <v>1</v>
       </c>
       <c r="CR26" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="CS26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CT26" t="n">
         <v>1</v>
@@ -12698,70 +12714,70 @@
         <v>14</v>
       </c>
       <c r="CV26" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY26" t="n">
         <v>15</v>
       </c>
-      <c r="CW26" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX26" t="n">
-        <v>3</v>
-      </c>
-      <c r="CY26" t="n">
-        <v>12</v>
-      </c>
       <c r="CZ26" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA26" t="n">
         <v>100</v>
       </c>
       <c r="DB26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="DE26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DF26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DG26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DH26" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DI26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DJ26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK26" t="n">
         <v>0</v>
       </c>
       <c r="DL26" t="n">
-        <v>3.13</v>
+        <v>1.09</v>
       </c>
       <c r="DM26" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="DN26" t="n">
-        <v>4.39</v>
+        <v>2.3</v>
       </c>
       <c r="DO26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
       </c>
       <c r="DQ26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR26" t="b">
         <v>0</v>
@@ -12780,22 +12796,22 @@
       </c>
       <c r="DW26" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="DX26" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="DY26" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="DZ26" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EA26" t="inlineStr">
@@ -12805,57 +12821,41 @@
       </c>
       <c r="EB26" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC26" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="ED26" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EE26" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EF26" t="inlineStr">
         <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EG26" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="EH26" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EI26" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EJ26" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="EG26" t="inlineStr"/>
+      <c r="EH26" t="inlineStr"/>
+      <c r="EI26" t="inlineStr"/>
+      <c r="EJ26" t="inlineStr"/>
       <c r="EK26" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EL26" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.32</t>
         </is>
       </c>
     </row>
@@ -13219,7 +13219,7 @@
         <v>2.3</v>
       </c>
       <c r="DO27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13675,7 +13675,7 @@
         <v>2.28</v>
       </c>
       <c r="DO28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -14131,7 +14131,7 @@
         <v>4.58</v>
       </c>
       <c r="DO29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -14571,7 +14571,7 @@
         <v>3.67</v>
       </c>
       <c r="DO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP30" t="b">
         <v>1</v>
@@ -14981,7 +14981,7 @@
         <v>1.5</v>
       </c>
       <c r="DE31" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DF31" t="n">
         <v>3</v>
@@ -15011,7 +15011,7 @@
         <v>1.51</v>
       </c>
       <c r="DO31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15131,12 +15131,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -15152,111 +15152,119 @@
         <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
+        <v>12</v>
+      </c>
+      <c r="L32" t="n">
+        <v>19</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>7</v>
       </c>
-      <c r="L32" t="n">
-        <v>9</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3</v>
-      </c>
       <c r="R32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V32" t="n">
         <v>18</v>
       </c>
       <c r="W32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="X32" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Z32" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
+        </is>
+      </c>
       <c r="AC32" t="n">
         <v>5</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.17</v>
+        <v>2.97</v>
       </c>
       <c r="AF32" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO32" t="n">
         <v>2.3</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>3</v>
-      </c>
       <c r="AP32" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR32" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AU32" t="n">
         <v>2</v>
@@ -15265,19 +15273,19 @@
         <v>1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX32" t="n">
         <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB32" t="n">
         <v>-1</v>
@@ -15286,13 +15294,13 @@
         <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE32" t="n">
         <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>-1</v>
+        <v>21687</v>
       </c>
       <c r="BG32" t="n">
         <v>2</v>
@@ -15304,61 +15312,61 @@
         <v>2</v>
       </c>
       <c r="BJ32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BK32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BL32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT32" t="n">
         <v>5</v>
       </c>
-      <c r="BM32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP32" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ32" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT32" t="n">
-        <v>3</v>
-      </c>
       <c r="BU32" t="n">
         <v>1</v>
       </c>
       <c r="BV32" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="BW32" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="BX32" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="BY32" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="BZ32" t="n">
-        <v>0.89</v>
+        <v>1.38</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="CB32" t="n">
-        <v>2.83</v>
+        <v>3.17</v>
       </c>
       <c r="CC32" t="n">
         <v>0</v>
@@ -15388,7 +15396,7 @@
         <v>0</v>
       </c>
       <c r="CL32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM32" t="n">
         <v>1</v>
@@ -15406,76 +15414,76 @@
         <v>1</v>
       </c>
       <c r="CR32" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CS32" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="CT32" t="n">
         <v>1</v>
       </c>
       <c r="CU32" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV32" t="n">
         <v>16</v>
       </c>
-      <c r="CV32" t="n">
-        <v>18</v>
-      </c>
       <c r="CW32" t="n">
         <v>1</v>
       </c>
       <c r="CX32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CY32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CZ32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DA32" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DB32" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC32" t="n">
         <v>100</v>
       </c>
       <c r="DD32" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DE32" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DF32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DG32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DH32" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DI32" t="n">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="DJ32" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DK32" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DL32" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="DM32" t="n">
-        <v>0.66</v>
+        <v>1.04</v>
       </c>
       <c r="DN32" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="DO32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DP32" t="b">
         <v>1</v>
@@ -15500,44 +15508,52 @@
       </c>
       <c r="DW32" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="DX32" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="DY32" t="inlineStr">
         <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="DZ32" t="inlineStr"/>
-      <c r="EA32" t="inlineStr"/>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="DZ32" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EA32" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
       <c r="EB32" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EC32" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="ED32" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EE32" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EF32" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EG32" t="inlineStr"/>
@@ -15563,12 +15579,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -15584,119 +15600,111 @@
         <v>2</v>
       </c>
       <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
         <v>7</v>
       </c>
-      <c r="K33" t="n">
-        <v>12</v>
-      </c>
       <c r="L33" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="U33" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="V33" t="n">
         <v>18</v>
       </c>
       <c r="W33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y33" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Z33" t="n">
-        <v>59</v>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Estádio Estadual Jornalista Edgar Augusto Proença</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>Rodovia Augusto Montenegro 3101, Mangueirão, Belém, Pará</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.97</v>
+        <v>2.17</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AU33" t="n">
         <v>2</v>
@@ -15705,19 +15713,19 @@
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB33" t="n">
         <v>-1</v>
@@ -15726,13 +15734,13 @@
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>21687</v>
+        <v>-1</v>
       </c>
       <c r="BG33" t="n">
         <v>2</v>
@@ -15744,175 +15752,175 @@
         <v>2</v>
       </c>
       <c r="BJ33" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="BK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL33" t="n">
         <v>5</v>
       </c>
-      <c r="BL33" t="n">
+      <c r="BM33" t="n">
         <v>4</v>
       </c>
-      <c r="BM33" t="n">
-        <v>10</v>
-      </c>
       <c r="BN33" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>33</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>53</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>61</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>98</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
         <v>9</v>
       </c>
-      <c r="BO33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT33" t="n">
+      <c r="CY33" t="n">
         <v>5</v>
       </c>
-      <c r="BU33" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV33" t="n">
-        <v>27</v>
-      </c>
-      <c r="BW33" t="n">
-        <v>51</v>
-      </c>
-      <c r="BX33" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY33" t="n">
-        <v>106</v>
-      </c>
-      <c r="BZ33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CA33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CB33" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="CC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS33" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU33" t="n">
-        <v>14</v>
-      </c>
-      <c r="CV33" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DA33" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="DB33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC33" t="n">
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="DE33" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="DF33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DG33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DH33" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DI33" t="n">
-        <v>0.33</v>
+        <v>2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DK33" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.04</v>
+        <v>0.66</v>
       </c>
       <c r="DN33" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="DO33" t="n">
         <v>5</v>
@@ -15940,52 +15948,44 @@
       </c>
       <c r="DW33" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="DX33" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="DZ33" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EA33" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="DZ33" t="inlineStr"/>
+      <c r="EA33" t="inlineStr"/>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EF33" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG33" t="inlineStr"/>
@@ -16330,10 +16330,10 @@
         <v>50</v>
       </c>
       <c r="DD34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE34" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DF34" t="n">
         <v>0</v>
@@ -16363,7 +16363,7 @@
         <v>1.6</v>
       </c>
       <c r="DO34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP34" t="b">
         <v>1</v>
@@ -16802,10 +16802,10 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DE35" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DF35" t="n">
         <v>0</v>
@@ -16835,7 +16835,7 @@
         <v>2.35</v>
       </c>
       <c r="DO35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17299,7 +17299,7 @@
         <v>3.37</v>
       </c>
       <c r="DO36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18186,10 +18186,10 @@
         <v>100</v>
       </c>
       <c r="DD38" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DF38" t="n">
         <v>1</v>
@@ -18219,7 +18219,7 @@
         <v>2.39</v>
       </c>
       <c r="DO38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18667,7 +18667,7 @@
         <v>3.58</v>
       </c>
       <c r="DO39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -19095,7 +19095,7 @@
         <v>3</v>
       </c>
       <c r="DO40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP40" t="b">
         <v>1</v>
@@ -19567,7 +19567,7 @@
         <v>2.92</v>
       </c>
       <c r="DO41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20039,7 +20039,7 @@
         <v>2.59</v>
       </c>
       <c r="DO42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -20487,7 +20487,7 @@
         <v>3.28</v>
       </c>
       <c r="DO43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -20959,7 +20959,7 @@
         <v>3.29</v>
       </c>
       <c r="DO44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP44" t="b">
         <v>1</v>
@@ -21224,7 +21224,7 @@
         <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>-1</v>
+        <v>17291</v>
       </c>
       <c r="BG45" t="n">
         <v>2</v>
@@ -21407,7 +21407,7 @@
         <v>4.22</v>
       </c>
       <c r="DO45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP45" t="b">
         <v>1</v>
@@ -21579,10 +21579,10 @@
         <v>7</v>
       </c>
       <c r="W46" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
         <v>63</v>
@@ -22415,6 +22415,4106 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Vitória</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>46095.89583333334</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10</v>
+      </c>
+      <c r="L48" t="n">
+        <v>14</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>3</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="n">
+        <v>9</v>
+      </c>
+      <c r="U48" t="n">
+        <v>9</v>
+      </c>
+      <c r="V48" t="n">
+        <v>12</v>
+      </c>
+      <c r="W48" t="n">
+        <v>17</v>
+      </c>
+      <c r="X48" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>33</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>67</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Estádio Manoel Barradas</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Rua Artêmio Castro Valente 1, Bairro Nossa Senhora da Vitória, Salvador, Bahia</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>610</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>7</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV48" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW48" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX48" t="n">
+        <v>80</v>
+      </c>
+      <c r="BY48" t="n">
+        <v>114</v>
+      </c>
+      <c r="BZ48" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CA48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CB48" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR48" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS48" t="n">
+        <v>28</v>
+      </c>
+      <c r="CT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU48" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV48" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW48" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX48" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY48" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ48" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA48" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB48" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC48" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD48" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH48" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI48" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ48" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK48" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL48" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DM48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="DN48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DO48" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ48" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV48" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW48" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="DX48" t="inlineStr">
+        <is>
+          <t>2.47</t>
+        </is>
+      </c>
+      <c r="DY48" t="inlineStr">
+        <is>
+          <t>3.39</t>
+        </is>
+      </c>
+      <c r="DZ48" t="inlineStr"/>
+      <c r="EA48" t="inlineStr"/>
+      <c r="EB48" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EC48" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
+      </c>
+      <c r="ED48" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EE48" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EF48" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EG48" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="EJ48" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="EK48" t="inlineStr"/>
+      <c r="EL48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>46095.97916666666</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>3</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" t="n">
+        <v>12</v>
+      </c>
+      <c r="U49" t="n">
+        <v>7</v>
+      </c>
+      <c r="V49" t="n">
+        <v>18</v>
+      </c>
+      <c r="W49" t="n">
+        <v>13</v>
+      </c>
+      <c r="X49" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Estádio Nilton Santos</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Rua Arquias Cordeiro, Engenho de Dentro, Rio de Janeiro</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>612</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>9</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>74</v>
+      </c>
+      <c r="BY49" t="n">
+        <v>123</v>
+      </c>
+      <c r="BZ49" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CA49" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CB49" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR49" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS49" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU49" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV49" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW49" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX49" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY49" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ49" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA49" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB49" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC49" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE49" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF49" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI49" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL49" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DM49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DN49" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DO49" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP49" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ49" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR49" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV49" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW49" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="DX49" t="inlineStr">
+        <is>
+          <t>4.47</t>
+        </is>
+      </c>
+      <c r="DY49" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DZ49" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EA49" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EB49" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EC49" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="ED49" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EE49" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EF49" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EG49" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EH49" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI49" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EJ49" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
+      <c r="EK49" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EL49" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>46096.79166666666</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>12</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>14</v>
+      </c>
+      <c r="V50" t="n">
+        <v>7</v>
+      </c>
+      <c r="W50" t="n">
+        <v>19</v>
+      </c>
+      <c r="X50" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>626</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>16574</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>66</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>18</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>117</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="CB50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR50" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS50" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU50" t="n">
+        <v>20</v>
+      </c>
+      <c r="CV50" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX50" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY50" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ50" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA50" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB50" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC50" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE50" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG50" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI50" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ50" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK50" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL50" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="DM50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="DN50" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="DO50" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP50" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV50" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW50" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="DX50" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="DY50" t="inlineStr">
+        <is>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="DZ50" t="inlineStr"/>
+      <c r="EA50" t="inlineStr"/>
+      <c r="EB50" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EC50" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="ED50" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EE50" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EF50" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EG50" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EH50" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI50" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EJ50" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EK50" t="inlineStr"/>
+      <c r="EL50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>46096.79166666666</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>10</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>14</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>24</v>
+      </c>
+      <c r="V51" t="n">
+        <v>4</v>
+      </c>
+      <c r="W51" t="n">
+        <v>13</v>
+      </c>
+      <c r="X51" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>617</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>47</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CB51" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR51" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS51" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU51" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV51" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX51" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY51" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ51" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA51" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC51" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD51" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF51" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG51" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH51" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DJ51" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK51" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL51" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="DM51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DN51" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DO51" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU51" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV51" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW51" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="DX51" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="DY51" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="DZ51" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EA51" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EB51" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EC51" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="ED51" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="EE51" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EF51" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EG51" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="EH51" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EI51" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ51" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EK51" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EL51" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>6</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>46096.79166666666</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" t="n">
+        <v>6</v>
+      </c>
+      <c r="L52" t="n">
+        <v>10</v>
+      </c>
+      <c r="M52" t="n">
+        <v>4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>3</v>
+      </c>
+      <c r="S52" t="n">
+        <v>7</v>
+      </c>
+      <c r="T52" t="n">
+        <v>7</v>
+      </c>
+      <c r="U52" t="n">
+        <v>11</v>
+      </c>
+      <c r="V52" t="n">
+        <v>10</v>
+      </c>
+      <c r="W52" t="n">
+        <v>20</v>
+      </c>
+      <c r="X52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Estádio Urbano Caldeira</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>16574</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CB52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR52" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS52" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU52" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV52" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX52" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY52" t="n">
+        <v>8</v>
+      </c>
+      <c r="CZ52" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA52" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB52" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC52" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DF52" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG52" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI52" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ52" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK52" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DM52" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DN52" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DO52" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP52" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ52" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU52" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV52" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW52" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="DX52" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="DY52" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="DZ52" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EA52" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EB52" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC52" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="ED52" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="EE52" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EF52" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EG52" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EH52" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EI52" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EJ52" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EK52" t="inlineStr"/>
+      <c r="EL52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>6</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>46096.89583333334</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="n">
+        <v>10</v>
+      </c>
+      <c r="U53" t="n">
+        <v>11</v>
+      </c>
+      <c r="V53" t="n">
+        <v>12</v>
+      </c>
+      <c r="W53" t="n">
+        <v>12</v>
+      </c>
+      <c r="X53" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Allianz Parque</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>619</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>35360</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>67</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>117</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>10</v>
+      </c>
+      <c r="CY53" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ53" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA53" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB53" t="n">
+        <v>100</v>
+      </c>
+      <c r="DC53" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD53" t="n">
+        <v>3</v>
+      </c>
+      <c r="DE53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG53" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH53" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL53" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="DM53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN53" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DO53" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP53" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV53" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW53" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="DX53" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="DY53" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="DZ53" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EA53" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EB53" t="inlineStr"/>
+      <c r="EC53" t="inlineStr"/>
+      <c r="ED53" t="inlineStr"/>
+      <c r="EE53" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF53" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG53" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EH53" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI53" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EJ53" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="EK53" t="inlineStr"/>
+      <c r="EL53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46096.89583333334</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="n">
+        <v>6</v>
+      </c>
+      <c r="L54" t="n">
+        <v>10</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>4</v>
+      </c>
+      <c r="T54" t="n">
+        <v>13</v>
+      </c>
+      <c r="U54" t="n">
+        <v>8</v>
+      </c>
+      <c r="V54" t="n">
+        <v>14</v>
+      </c>
+      <c r="W54" t="n">
+        <v>13</v>
+      </c>
+      <c r="X54" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Estádio Major Antônio Couto Pereira</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>627</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>37</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>51</v>
+      </c>
+      <c r="BY54" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ54" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CA54" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CB54" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR54" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>15</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV54" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX54" t="n">
+        <v>15</v>
+      </c>
+      <c r="CY54" t="n">
+        <v>3</v>
+      </c>
+      <c r="CZ54" t="n">
+        <v>25</v>
+      </c>
+      <c r="DA54" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB54" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC54" t="n">
+        <v>25</v>
+      </c>
+      <c r="DD54" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE54" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG54" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DI54" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DJ54" t="n">
+        <v>75</v>
+      </c>
+      <c r="DK54" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL54" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DM54" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN54" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="DO54" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP54" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV54" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW54" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="DX54" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="DY54" t="inlineStr">
+        <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="DZ54" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EA54" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EB54" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EF54" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG54" t="inlineStr"/>
+      <c r="EH54" t="inlineStr"/>
+      <c r="EI54" t="inlineStr"/>
+      <c r="EJ54" t="inlineStr"/>
+      <c r="EK54" t="inlineStr"/>
+      <c r="EL54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46096.97916666666</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" t="n">
+        <v>10</v>
+      </c>
+      <c r="M55" t="n">
+        <v>4</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>13</v>
+      </c>
+      <c r="V55" t="n">
+        <v>4</v>
+      </c>
+      <c r="W55" t="n">
+        <v>5</v>
+      </c>
+      <c r="X55" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>618</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>6</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>5</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY55" t="n">
+        <v>71</v>
+      </c>
+      <c r="BZ55" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CA55" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CB55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR55" t="n">
+        <v>24</v>
+      </c>
+      <c r="CS55" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU55" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV55" t="n">
+        <v>18</v>
+      </c>
+      <c r="CW55" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX55" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY55" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA55" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC55" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DE55" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DF55" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG55" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH55" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DJ55" t="n">
+        <v>100</v>
+      </c>
+      <c r="DK55" t="n">
+        <v>50</v>
+      </c>
+      <c r="DL55" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="DM55" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="DN55" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DO55" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS55" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT55" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU55" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV55" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW55" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="DX55" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="DY55" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="DZ55" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EA55" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>4.38</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EG55" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr"/>
+      <c r="EL55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>46096.97916666666</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>6</v>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" t="n">
+        <v>9</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>6</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7</v>
+      </c>
+      <c r="S56" t="n">
+        <v>14</v>
+      </c>
+      <c r="T56" t="n">
+        <v>8</v>
+      </c>
+      <c r="U56" t="n">
+        <v>20</v>
+      </c>
+      <c r="V56" t="n">
+        <v>15</v>
+      </c>
+      <c r="W56" t="n">
+        <v>2</v>
+      </c>
+      <c r="X56" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Estádio Governador Magalhães Pinto</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Avenida Antonio Abrahão Carã 1001, Pampulhas, Belo Horizonte, Minas Gerais</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>100</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>12</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>4</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>91</v>
+      </c>
+      <c r="BY56" t="n">
+        <v>86</v>
+      </c>
+      <c r="BZ56" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CA56" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB56" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR56" t="n">
+        <v>10</v>
+      </c>
+      <c r="CS56" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU56" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV56" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW56" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX56" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY56" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ56" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA56" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB56" t="n">
+        <v>75</v>
+      </c>
+      <c r="DC56" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD56" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DE56" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI56" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DJ56" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL56" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DM56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DN56" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO56" t="n">
+        <v>6</v>
+      </c>
+      <c r="DP56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DV56" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW56" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="DX56" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="DY56" t="inlineStr">
+        <is>
+          <t>4.48</t>
+        </is>
+      </c>
+      <c r="DZ56" t="inlineStr"/>
+      <c r="EA56" t="inlineStr"/>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>3.96</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EG56" t="inlineStr"/>
+      <c r="EH56" t="inlineStr"/>
+      <c r="EI56" t="inlineStr"/>
+      <c r="EJ56" t="inlineStr"/>
+      <c r="EK56" t="inlineStr"/>
+      <c r="EL56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL56" headerRowCount="1">
-  <autoFilter ref="A1:EL56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL57" headerRowCount="1">
+  <autoFilter ref="A1:EL57"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL56"/>
+  <dimension ref="A1:EL57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -3569,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP6" t="b">
         <v>1</v>
@@ -4486,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE8" t="n">
         <v>0.33</v>
@@ -4519,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -9575,7 +9575,7 @@
         <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -11346,7 +11346,7 @@
         <v>100</v>
       </c>
       <c r="DD23" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE23" t="n">
         <v>2.33</v>
@@ -11379,7 +11379,7 @@
         <v>1.86</v>
       </c>
       <c r="DO23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP23" t="b">
         <v>1</v>
@@ -12741,7 +12741,7 @@
         <v>3</v>
       </c>
       <c r="DE26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="DF26" t="n">
         <v>3</v>
@@ -12771,7 +12771,7 @@
         <v>2.3</v>
       </c>
       <c r="DO26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -17763,7 +17763,7 @@
         <v>2.85</v>
       </c>
       <c r="DO37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP37" t="b">
         <v>1</v>
@@ -21871,7 +21871,7 @@
         <v>2.06</v>
       </c>
       <c r="DO46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="DP46" t="b">
         <v>1</v>
@@ -22311,7 +22311,7 @@
         <v>3.91</v>
       </c>
       <c r="DO47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -23359,291 +23359,299 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>46096.79166666666</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
+        <v>10</v>
+      </c>
+      <c r="M50" t="n">
+        <v>4</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4</v>
+      </c>
+      <c r="S50" t="n">
         <v>8</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>2</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>12</v>
       </c>
       <c r="T50" t="n">
         <v>6</v>
       </c>
       <c r="U50" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="V50" t="n">
+        <v>10</v>
+      </c>
+      <c r="W50" t="n">
+        <v>20</v>
+      </c>
+      <c r="X50" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Estádio Urbano Caldeira</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>15008</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM50" t="n">
         <v>7</v>
       </c>
-      <c r="W50" t="n">
+      <c r="BN50" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW50" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX50" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY50" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA50" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB50" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR50" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS50" t="n">
         <v>19</v>
       </c>
-      <c r="X50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>53</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>626</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>16574</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI50" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK50" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM50" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN50" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO50" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP50" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS50" t="n">
-        <v>4</v>
-      </c>
-      <c r="BT50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV50" t="n">
-        <v>66</v>
-      </c>
-      <c r="BW50" t="n">
-        <v>18</v>
-      </c>
-      <c r="BX50" t="n">
-        <v>117</v>
-      </c>
-      <c r="BY50" t="n">
-        <v>64</v>
-      </c>
-      <c r="BZ50" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CA50" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="CB50" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI50" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ50" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM50" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN50" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP50" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ50" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>31</v>
-      </c>
-      <c r="CS50" t="n">
-        <v>16</v>
-      </c>
       <c r="CT50" t="n">
         <v>1</v>
       </c>
       <c r="CU50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="CV50" t="n">
         <v>20</v>
@@ -23652,64 +23660,64 @@
         <v>1</v>
       </c>
       <c r="CX50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CY50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="CZ50" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DA50" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB50" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DC50" t="n">
         <v>100</v>
       </c>
       <c r="DD50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="DE50" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="DF50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DG50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DH50" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="DI50" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="DJ50" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK50" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DL50" t="n">
-        <v>2.23</v>
+        <v>1.12</v>
       </c>
       <c r="DM50" t="n">
-        <v>1.09</v>
+        <v>0.44</v>
       </c>
       <c r="DN50" t="n">
-        <v>3.32</v>
+        <v>1.56</v>
       </c>
       <c r="DO50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
       </c>
       <c r="DQ50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR50" t="b">
         <v>0</v>
@@ -23724,68 +23732,76 @@
         <v>0</v>
       </c>
       <c r="DV50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW50" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DX50" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="DY50" t="inlineStr">
         <is>
-          <t>4.49</t>
-        </is>
-      </c>
-      <c r="DZ50" t="inlineStr"/>
-      <c r="EA50" t="inlineStr"/>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="DZ50" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EA50" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
       <c r="EB50" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC50" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="ED50" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EE50" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EF50" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EG50" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="EH50" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EI50" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EJ50" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EK50" t="inlineStr"/>
@@ -23807,25 +23823,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>46096.79166666666</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>7</v>
@@ -23837,126 +23853,126 @@
         <v>8</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="n">
+        <v>6</v>
+      </c>
+      <c r="U51" t="n">
         <v>14</v>
       </c>
-      <c r="T51" t="n">
-        <v>2</v>
-      </c>
-      <c r="U51" t="n">
-        <v>24</v>
-      </c>
       <c r="V51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W51" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="X51" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Y51" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="Z51" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AF51" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AG51" t="n">
-        <v>4.84</v>
+        <v>4</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AJ51" t="n">
-        <v>3.54</v>
+        <v>2.72</v>
       </c>
       <c r="AK51" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AO51" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AU51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
         <v>1</v>
       </c>
       <c r="AX51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB51" t="n">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="BC51" t="n">
         <v>0</v>
@@ -23968,7 +23984,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>-1</v>
+        <v>16574</v>
       </c>
       <c r="BG51" t="n">
         <v>2</v>
@@ -23977,64 +23993,64 @@
         <v>1</v>
       </c>
       <c r="BI51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS51" t="n">
         <v>4</v>
       </c>
-      <c r="BL51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM51" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN51" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR51" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS51" t="n">
-        <v>2</v>
-      </c>
       <c r="BT51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU51" t="n">
         <v>1</v>
       </c>
       <c r="BV51" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="BW51" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BX51" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BY51" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="BZ51" t="n">
-        <v>2.73</v>
+        <v>1.51</v>
       </c>
       <c r="CA51" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="CB51" t="n">
-        <v>3.23</v>
+        <v>2.15</v>
       </c>
       <c r="CC51" t="n">
         <v>0</v>
@@ -24061,16 +24077,16 @@
         <v>1</v>
       </c>
       <c r="CK51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO51" t="n">
         <v>0</v>
@@ -24082,73 +24098,73 @@
         <v>1</v>
       </c>
       <c r="CR51" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="CS51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="CT51" t="n">
         <v>1</v>
       </c>
       <c r="CU51" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="CV51" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="CW51" t="n">
         <v>1</v>
       </c>
       <c r="CX51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CY51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="CZ51" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA51" t="n">
         <v>50</v>
       </c>
       <c r="DB51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC51" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE51" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG51" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DI51" t="n">
+        <v>2</v>
+      </c>
+      <c r="DJ51" t="n">
         <v>50</v>
-      </c>
-      <c r="DD51" t="n">
-        <v>3</v>
-      </c>
-      <c r="DE51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DF51" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG51" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH51" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DJ51" t="n">
-        <v>75</v>
       </c>
       <c r="DK51" t="n">
         <v>50</v>
       </c>
       <c r="DL51" t="n">
-        <v>1.27</v>
+        <v>2.23</v>
       </c>
       <c r="DM51" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="DN51" t="n">
-        <v>2.57</v>
+        <v>3.32</v>
       </c>
       <c r="DO51" t="n">
         <v>5</v>
@@ -24157,103 +24173,87 @@
         <v>1</v>
       </c>
       <c r="DQ51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU51" t="b">
         <v>0</v>
       </c>
       <c r="DV51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW51" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="DX51" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="DY51" t="inlineStr">
         <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="DZ51" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EA51" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
+          <t>4.49</t>
+        </is>
+      </c>
+      <c r="DZ51" t="inlineStr"/>
+      <c r="EA51" t="inlineStr"/>
       <c r="EB51" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EC51" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="ED51" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EE51" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EF51" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="EG51" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="EH51" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EI51" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EJ51" t="inlineStr">
         <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EK51" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EL51" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EK51" t="inlineStr"/>
+      <c r="EL51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -24271,104 +24271,96 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>46096.79166666666</v>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J52" t="n">
+        <v>7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>10</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>14</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>24</v>
+      </c>
+      <c r="V52" t="n">
         <v>4</v>
       </c>
-      <c r="K52" t="n">
-        <v>6</v>
-      </c>
-      <c r="L52" t="n">
-        <v>10</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4</v>
-      </c>
-      <c r="R52" t="n">
-        <v>3</v>
-      </c>
-      <c r="S52" t="n">
-        <v>7</v>
-      </c>
-      <c r="T52" t="n">
-        <v>7</v>
-      </c>
-      <c r="U52" t="n">
+      <c r="W52" t="n">
+        <v>13</v>
+      </c>
+      <c r="X52" t="n">
         <v>11</v>
       </c>
-      <c r="V52" t="n">
-        <v>10</v>
-      </c>
-      <c r="W52" t="n">
-        <v>20</v>
-      </c>
-      <c r="X52" t="n">
-        <v>15</v>
-      </c>
       <c r="Y52" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="Z52" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Estádio Urbano Caldeira</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD52" t="n">
         <v>5</v>
       </c>
-      <c r="AD52" t="n">
-        <v>2</v>
-      </c>
       <c r="AE52" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AF52" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG52" t="n">
-        <v>3.25</v>
+        <v>4.84</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI52" t="n">
         <v>2.1</v>
@@ -24377,71 +24369,71 @@
         <v>3.54</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AM52" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ52" t="n">
         <v>1.41</v>
       </c>
-      <c r="AN52" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR52" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AU52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW52" t="n">
         <v>1</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB52" t="n">
+        <v>617</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
         <v>-1</v>
       </c>
-      <c r="BC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>16574</v>
-      </c>
       <c r="BG52" t="n">
         <v>2</v>
       </c>
@@ -24452,178 +24444,178 @@
         <v>3</v>
       </c>
       <c r="BJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK52" t="n">
         <v>4</v>
       </c>
-      <c r="BK52" t="n">
-        <v>1</v>
-      </c>
       <c r="BL52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>47</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CB52" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR52" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS52" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU52" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV52" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX52" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY52" t="n">
         <v>7</v>
-      </c>
-      <c r="BN52" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ52" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS52" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT52" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV52" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW52" t="n">
-        <v>33</v>
-      </c>
-      <c r="BX52" t="n">
-        <v>92</v>
-      </c>
-      <c r="BY52" t="n">
-        <v>77</v>
-      </c>
-      <c r="BZ52" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CA52" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="CB52" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS52" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU52" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV52" t="n">
-        <v>20</v>
-      </c>
-      <c r="CW52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX52" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY52" t="n">
-        <v>8</v>
       </c>
       <c r="CZ52" t="n">
         <v>25</v>
       </c>
       <c r="DA52" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB52" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DC52" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="DF52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG52" t="n">
         <v>2</v>
       </c>
       <c r="DH52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DI52" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="DJ52" t="n">
         <v>75</v>
       </c>
       <c r="DK52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL52" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="DM52" t="n">
-        <v>0.44</v>
+        <v>1.3</v>
       </c>
       <c r="DN52" t="n">
-        <v>1.56</v>
+        <v>2.57</v>
       </c>
       <c r="DO52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24632,13 +24624,13 @@
         <v>1</v>
       </c>
       <c r="DR52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU52" t="b">
         <v>0</v>
@@ -24648,76 +24640,84 @@
       </c>
       <c r="DW52" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="DX52" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="DY52" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="DZ52" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EA52" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB52" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC52" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="ED52" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EE52" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EF52" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EG52" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EH52" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI52" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ52" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EK52" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="EJ52" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EK52" t="inlineStr"/>
-      <c r="EL52" t="inlineStr"/>
+      <c r="EL52" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -24735,12 +24735,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -24756,16 +24756,16 @@
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L53" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53" t="n">
         <v>3</v>
@@ -24780,95 +24780,95 @@
         <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T53" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="V53" t="n">
+        <v>14</v>
+      </c>
+      <c r="W53" t="n">
+        <v>13</v>
+      </c>
+      <c r="X53" t="n">
         <v>12</v>
       </c>
-      <c r="W53" t="n">
-        <v>12</v>
-      </c>
-      <c r="X53" t="n">
-        <v>15</v>
-      </c>
       <c r="Y53" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Allianz Parque</t>
+          <t>Estádio Major Antônio Couto Pereira</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
+          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD53" t="n">
         <v>3</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AF53" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="AG53" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="AK53" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL53" t="n">
         <v>1.78</v>
       </c>
-      <c r="AL53" t="n">
-        <v>2</v>
-      </c>
       <c r="AM53" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AN53" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AO53" t="n">
-        <v>3.33</v>
+        <v>3.22</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="AS53" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AU53" t="n">
         <v>1</v>
@@ -24892,19 +24892,19 @@
         <v>1</v>
       </c>
       <c r="BB53" t="n">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="BC53" t="n">
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>35360</v>
+        <v>-1</v>
       </c>
       <c r="BG53" t="n">
         <v>2</v>
@@ -24916,37 +24916,37 @@
         <v>1</v>
       </c>
       <c r="BJ53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ53" t="n">
         <v>1</v>
       </c>
       <c r="BR53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS53" t="n">
         <v>2</v>
       </c>
       <c r="BT53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU53" t="n">
         <v>1</v>
@@ -24955,22 +24955,22 @@
         <v>37</v>
       </c>
       <c r="BW53" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="BX53" t="n">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="BY53" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="BZ53" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="CA53" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="CB53" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="CC53" t="n">
         <v>0</v>
@@ -25006,7 +25006,7 @@
         <v>1</v>
       </c>
       <c r="CN53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO53" t="n">
         <v>0</v>
@@ -25018,76 +25018,76 @@
         <v>1</v>
       </c>
       <c r="CR53" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="CS53" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CT53" t="n">
         <v>1</v>
       </c>
       <c r="CU53" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="CV53" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CW53" t="n">
         <v>1</v>
       </c>
       <c r="CX53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="CY53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="CZ53" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="DA53" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB53" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="DC53" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="DD53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="DE53" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG53" t="n">
         <v>0.5</v>
       </c>
-      <c r="DF53" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG53" t="n">
-        <v>1</v>
-      </c>
       <c r="DH53" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="DI53" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="DJ53" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="DK53" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL53" t="n">
-        <v>1.77</v>
+        <v>1.08</v>
       </c>
       <c r="DM53" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="DN53" t="n">
-        <v>2.78</v>
+        <v>2.51</v>
       </c>
       <c r="DO53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DP53" t="b">
         <v>1</v>
@@ -25112,32 +25112,44 @@
       </c>
       <c r="DW53" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="DX53" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="EB53" t="inlineStr"/>
-      <c r="EC53" t="inlineStr"/>
-      <c r="ED53" t="inlineStr"/>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EB53" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>1.99</t>
+        </is>
+      </c>
       <c r="EE53" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -25145,29 +25157,13 @@
       </c>
       <c r="EF53" t="inlineStr">
         <is>
-          <t>2.01</t>
-        </is>
-      </c>
-      <c r="EG53" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="EH53" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI53" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EJ53" t="inlineStr">
-        <is>
-          <t>3.28</t>
-        </is>
-      </c>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EG53" t="inlineStr"/>
+      <c r="EH53" t="inlineStr"/>
+      <c r="EI53" t="inlineStr"/>
+      <c r="EJ53" t="inlineStr"/>
       <c r="EK53" t="inlineStr"/>
       <c r="EL53" t="inlineStr"/>
     </row>
@@ -25187,12 +25183,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -25208,13 +25204,13 @@
         <v>1</v>
       </c>
       <c r="J54" t="n">
+        <v>2</v>
+      </c>
+      <c r="K54" t="n">
         <v>4</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>6</v>
-      </c>
-      <c r="L54" t="n">
-        <v>10</v>
       </c>
       <c r="M54" t="n">
         <v>2</v>
@@ -25232,40 +25228,40 @@
         <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T54" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U54" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="V54" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W54" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X54" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Y54" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z54" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Estádio Major Antônio Couto Pereira</t>
+          <t>Allianz Parque</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Rua Ubaldino do Amaral 37, Bairro Alto da Glória, Curitiba, Paraná</t>
+          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
         </is>
       </c>
       <c r="AC54" t="n">
@@ -25275,52 +25271,52 @@
         <v>3</v>
       </c>
       <c r="AE54" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI54" t="n">
         <v>1.72</v>
       </c>
-      <c r="AF54" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ54" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AL54" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AN54" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AO54" t="n">
-        <v>3.22</v>
+        <v>3.33</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AR54" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AS54" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU54" t="n">
         <v>1</v>
@@ -25344,19 +25340,19 @@
         <v>1</v>
       </c>
       <c r="BB54" t="n">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="BC54" t="n">
         <v>0</v>
       </c>
       <c r="BD54" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="BE54" t="n">
         <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>-1</v>
+        <v>35360</v>
       </c>
       <c r="BG54" t="n">
         <v>2</v>
@@ -25368,31 +25364,31 @@
         <v>1</v>
       </c>
       <c r="BJ54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN54" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BO54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS54" t="n">
         <v>2</v>
@@ -25407,22 +25403,22 @@
         <v>37</v>
       </c>
       <c r="BW54" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="BX54" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="BY54" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="BZ54" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="CA54" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="CB54" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="CC54" t="n">
         <v>0</v>
@@ -25458,7 +25454,7 @@
         <v>1</v>
       </c>
       <c r="CN54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO54" t="n">
         <v>0</v>
@@ -25470,76 +25466,76 @@
         <v>1</v>
       </c>
       <c r="CR54" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS54" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU54" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV54" t="n">
         <v>14</v>
       </c>
-      <c r="CS54" t="n">
-        <v>15</v>
-      </c>
-      <c r="CT54" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU54" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV54" t="n">
-        <v>13</v>
-      </c>
       <c r="CW54" t="n">
         <v>1</v>
       </c>
       <c r="CX54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CY54" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ54" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DA54" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB54" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DC54" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="DD54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DE54" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DH54" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="DI54" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="DJ54" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="DK54" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL54" t="n">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="DM54" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="DN54" t="n">
-        <v>2.51</v>
+        <v>2.78</v>
       </c>
       <c r="DO54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -25564,44 +25560,32 @@
       </c>
       <c r="DW54" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="DX54" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="DY54" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="DZ54" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EA54" t="inlineStr">
         <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="EB54" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
-      <c r="EC54" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="ED54" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="EB54" t="inlineStr"/>
+      <c r="EC54" t="inlineStr"/>
+      <c r="ED54" t="inlineStr"/>
       <c r="EE54" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -25609,13 +25593,29 @@
       </c>
       <c r="EF54" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EG54" t="inlineStr"/>
-      <c r="EH54" t="inlineStr"/>
-      <c r="EI54" t="inlineStr"/>
-      <c r="EJ54" t="inlineStr"/>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EG54" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EH54" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI54" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EJ54" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
       <c r="EK54" t="inlineStr"/>
       <c r="EL54" t="inlineStr"/>
     </row>
@@ -25695,10 +25695,10 @@
         <v>4</v>
       </c>
       <c r="W55" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="X55" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Y55" t="n">
         <v>50</v>
@@ -26151,16 +26151,16 @@
         <v>15</v>
       </c>
       <c r="W56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="X56" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Y56" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Z56" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
@@ -26481,8 +26481,16 @@
           <t>4.48</t>
         </is>
       </c>
-      <c r="DZ56" t="inlineStr"/>
-      <c r="EA56" t="inlineStr"/>
+      <c r="DZ56" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EA56" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
       <c r="EB56" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -26514,6 +26522,462 @@
       <c r="EJ56" t="inlineStr"/>
       <c r="EK56" t="inlineStr"/>
       <c r="EL56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46097.95833333334</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" t="n">
+        <v>9</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="n">
+        <v>9</v>
+      </c>
+      <c r="U57" t="n">
+        <v>11</v>
+      </c>
+      <c r="V57" t="n">
+        <v>13</v>
+      </c>
+      <c r="W57" t="n">
+        <v>15</v>
+      </c>
+      <c r="X57" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Arena Condá</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Rua Clevelândia, Bairro Centro, Chapecó, Santa Catarina</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>19307</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>66</v>
+      </c>
+      <c r="BY57" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ57" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CA57" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CC57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP57" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR57" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS57" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU57" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV57" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW57" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX57" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY57" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ57" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA57" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB57" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC57" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE57" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF57" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ57" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK57" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL57" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM57" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DN57" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DO57" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP57" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ57" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU57" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV57" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW57" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="DX57" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="DY57" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="DZ57" t="inlineStr"/>
+      <c r="EA57" t="inlineStr"/>
+      <c r="EB57" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="EC57" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
+      <c r="ED57" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EE57" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF57" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EG57" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EH57" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI57" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EJ57" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="EK57" t="inlineStr"/>
+      <c r="EL57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -32455,7 +32455,7 @@
         <v>6</v>
       </c>
       <c r="W70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X70" t="n">
         <v>21</v>
@@ -32785,8 +32785,16 @@
           <t>2.95</t>
         </is>
       </c>
-      <c r="DZ70" t="inlineStr"/>
-      <c r="EA70" t="inlineStr"/>
+      <c r="DZ70" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EA70" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
       <c r="EB70" t="inlineStr">
         <is>
           <t>1.40</t>
@@ -32884,7 +32892,7 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -32917,10 +32925,10 @@
         <v>14</v>
       </c>
       <c r="Y71" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z71" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
@@ -32936,7 +32944,7 @@
         <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE71" t="n">
         <v>1.73</v>
@@ -33056,13 +33064,13 @@
         <v>0</v>
       </c>
       <c r="BR71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS71" t="n">
         <v>1</v>
       </c>
       <c r="BT71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU71" t="n">
         <v>1</v>
@@ -33134,7 +33142,7 @@
         <v>1</v>
       </c>
       <c r="CR71" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CS71" t="n">
         <v>22</v>
@@ -33228,42 +33236,42 @@
       </c>
       <c r="DW71" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="DX71" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="DY71" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="DZ71" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EA71" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EB71" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC71" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="ED71" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EE71" t="inlineStr">
@@ -33278,7 +33286,7 @@
       </c>
       <c r="EG71" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="EH71" t="inlineStr">
@@ -33293,7 +33301,7 @@
       </c>
       <c r="EJ71" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EK71" t="inlineStr"/>
@@ -33348,7 +33356,7 @@
         <v>2</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -33366,13 +33374,13 @@
         <v>6</v>
       </c>
       <c r="T72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U72" t="n">
         <v>16</v>
       </c>
       <c r="V72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W72" t="n">
         <v>13</v>
@@ -33400,7 +33408,7 @@
         <v>2</v>
       </c>
       <c r="AD72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE72" t="n">
         <v>3.3</v>
@@ -33520,13 +33528,13 @@
         <v>1</v>
       </c>
       <c r="BR72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS72" t="n">
         <v>1</v>
       </c>
       <c r="BT72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU72" t="n">
         <v>1</v>
@@ -33547,10 +33555,10 @@
         <v>1.91</v>
       </c>
       <c r="CA72" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="CB72" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="CC72" t="n">
         <v>0</v>
@@ -33692,72 +33700,64 @@
       </c>
       <c r="DW72" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="DX72" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="DY72" t="inlineStr">
         <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="DZ72" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="EA72" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="DZ72" t="inlineStr"/>
+      <c r="EA72" t="inlineStr"/>
       <c r="EB72" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EC72" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="ED72" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EE72" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EF72" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EG72" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EH72" t="inlineStr">
         <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI72" t="inlineStr">
+        <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="EI72" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
       <c r="EJ72" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EK72" t="inlineStr"/>
@@ -34148,64 +34148,64 @@
       </c>
       <c r="DW73" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="DX73" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="DY73" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="DZ73" t="inlineStr"/>
       <c r="EA73" t="inlineStr"/>
       <c r="EB73" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="EC73" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="ED73" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EE73" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EF73" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EG73" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EH73" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="EI73" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EJ73" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="EK73" t="inlineStr"/>
@@ -34275,16 +34275,16 @@
         <v>3</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U74" t="n">
+        <v>10</v>
+      </c>
+      <c r="V74" t="n">
         <v>9</v>
-      </c>
-      <c r="V74" t="n">
-        <v>10</v>
       </c>
       <c r="W74" t="n">
         <v>9</v>
@@ -34456,10 +34456,10 @@
         <v>121</v>
       </c>
       <c r="BZ74" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="CA74" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="CB74" t="n">
         <v>2.5</v>
@@ -34604,42 +34604,42 @@
       </c>
       <c r="DW74" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="DX74" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="DY74" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="DZ74" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EA74" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EB74" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="EC74" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="ED74" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EE74" t="inlineStr">
@@ -34649,7 +34649,7 @@
       </c>
       <c r="EF74" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EG74" t="inlineStr"/>
@@ -35052,7 +35052,7 @@
       </c>
       <c r="DW75" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="DX75" t="inlineStr">
@@ -35062,42 +35062,42 @@
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EG75" t="inlineStr"/>
@@ -35174,13 +35174,13 @@
         <v>7</v>
       </c>
       <c r="T76" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U76" t="n">
         <v>13</v>
       </c>
       <c r="V76" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W76" t="n">
         <v>15</v>
@@ -35355,10 +35355,10 @@
         <v>1.53</v>
       </c>
       <c r="CA76" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -35500,76 +35500,84 @@
       </c>
       <c r="DW76" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="DX76" t="inlineStr">
         <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="DY76" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="DZ76" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EA76" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EB76" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EC76" t="inlineStr">
+        <is>
+          <t>4.53</t>
+        </is>
+      </c>
+      <c r="ED76" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EF76" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EG76" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="EH76" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EJ76" t="inlineStr">
+        <is>
           <t>2.67</t>
         </is>
       </c>
-      <c r="DY76" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="DZ76" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EA76" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EB76" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="EC76" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="ED76" t="inlineStr">
-        <is>
-          <t>2.36</t>
-        </is>
-      </c>
-      <c r="EE76" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EF76" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EG76" t="inlineStr">
-        <is>
-          <t>3.43</t>
-        </is>
-      </c>
-      <c r="EH76" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EI76" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EJ76" t="inlineStr">
-        <is>
-          <t>2.72</t>
-        </is>
-      </c>
-      <c r="EK76" t="inlineStr"/>
-      <c r="EL76" t="inlineStr"/>
+      <c r="EK76" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -35617,7 +35625,7 @@
         <v>8</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N77" t="n">
         <v>3</v>
@@ -35635,22 +35643,22 @@
         <v>2</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T77" t="n">
         <v>8</v>
       </c>
       <c r="U77" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V77" t="n">
         <v>10</v>
       </c>
       <c r="W77" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="X77" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Y77" t="n">
         <v>54</v>
@@ -35669,7 +35677,7 @@
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD77" t="n">
         <v>5</v>
@@ -35789,7 +35797,7 @@
         <v>2</v>
       </c>
       <c r="BQ77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR77" t="n">
         <v>2</v>
@@ -35798,7 +35806,7 @@
         <v>2</v>
       </c>
       <c r="BT77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU77" t="n">
         <v>1</v>
@@ -35816,13 +35824,13 @@
         <v>74</v>
       </c>
       <c r="BZ77" t="n">
-        <v>0.98</v>
+        <v>1.04</v>
       </c>
       <c r="CA77" t="n">
         <v>0.8</v>
       </c>
       <c r="CB77" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="CC77" t="n">
         <v>0</v>
@@ -35964,52 +35972,52 @@
       </c>
       <c r="DW77" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="DX77" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EG77" t="inlineStr"/>
@@ -36018,12 +36026,12 @@
       <c r="EJ77" t="inlineStr"/>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EL77" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL77" headerRowCount="1">
-  <autoFilter ref="A1:EL77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL78" headerRowCount="1">
+  <autoFilter ref="A1:EL78"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL77"/>
+  <dimension ref="A1:EL78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31.2" customWidth="1" min="1" max="1"/>
@@ -1664,10 +1664,10 @@
         <v>1</v>
       </c>
       <c r="BV2" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="BW2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BX2" t="n">
         <v>121</v>
@@ -1676,13 +1676,13 @@
         <v>68</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP2" t="b">
         <v>1</v>
@@ -3936,10 +3936,10 @@
         <v>1</v>
       </c>
       <c r="BV7" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BW7" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="BX7" t="n">
         <v>48</v>
@@ -3948,13 +3948,13 @@
         <v>151</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.13</v>
+        <v>3.49</v>
       </c>
       <c r="CC7" t="n">
         <v>1</v>
@@ -4235,7 +4235,7 @@
         <v>11</v>
       </c>
       <c r="W8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -5117,7 +5117,7 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR10" t="n">
         <v>1</v>
@@ -5298,7 +5298,7 @@
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU10" t="n">
         <v>1</v>
@@ -5887,7 +5887,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -8617,7 +8617,7 @@
         <v>2.5</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP17" t="b">
         <v>1</v>
@@ -9440,10 +9440,10 @@
         <v>1</v>
       </c>
       <c r="BV19" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="BW19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BX19" t="n">
         <v>134</v>
@@ -9452,13 +9452,13 @@
         <v>57</v>
       </c>
       <c r="BZ19" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -10751,22 +10751,22 @@
         <v>4</v>
       </c>
       <c r="BO22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BP22" t="n">
         <v>2</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR22" t="n">
         <v>0</v>
       </c>
       <c r="BS22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BT22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU22" t="n">
         <v>1</v>
@@ -11370,13 +11370,13 @@
         <v>0</v>
       </c>
       <c r="DL23" t="n">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
       <c r="DM23" t="n">
         <v>1.02</v>
       </c>
       <c r="DN23" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="DO23" t="n">
         <v>7</v>
@@ -11551,10 +11551,10 @@
         <v>18</v>
       </c>
       <c r="W24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Y24" t="n">
         <v>59</v>
@@ -12433,7 +12433,7 @@
         <v>12</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
         <v>4</v>
@@ -12605,7 +12605,7 @@
         <v>2</v>
       </c>
       <c r="BQ26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR26" t="n">
         <v>2</v>
@@ -12614,7 +12614,7 @@
         <v>3</v>
       </c>
       <c r="BT26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU26" t="n">
         <v>1</v>
@@ -12746,13 +12746,13 @@
         <v>0</v>
       </c>
       <c r="DL26" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="DM26" t="n">
         <v>1.26</v>
       </c>
       <c r="DN26" t="n">
-        <v>4.39</v>
+        <v>4.64</v>
       </c>
       <c r="DO26" t="n">
         <v>7</v>
@@ -12935,10 +12935,10 @@
         <v>10</v>
       </c>
       <c r="W27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y27" t="n">
         <v>56</v>
@@ -13186,7 +13186,7 @@
         <v>50</v>
       </c>
       <c r="DD27" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DE27" t="n">
         <v>0.5</v>
@@ -13213,13 +13213,13 @@
         <v>0</v>
       </c>
       <c r="DM27" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="DN27" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="DO27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -13391,7 +13391,7 @@
         <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X28" t="n">
         <v>11</v>
@@ -13645,7 +13645,7 @@
         <v>3</v>
       </c>
       <c r="DE28" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF28" t="n">
         <v>3</v>
@@ -13675,7 +13675,7 @@
         <v>2.28</v>
       </c>
       <c r="DO28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -13839,10 +13839,10 @@
         <v>9</v>
       </c>
       <c r="W29" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="X29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
         <v>60</v>
@@ -14562,13 +14562,13 @@
         <v>50</v>
       </c>
       <c r="DL30" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="DM30" t="n">
         <v>1.57</v>
       </c>
       <c r="DN30" t="n">
-        <v>3.67</v>
+        <v>3.72</v>
       </c>
       <c r="DO30" t="n">
         <v>8</v>
@@ -14978,7 +14978,7 @@
         <v>50</v>
       </c>
       <c r="DD31" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DE31" t="n">
         <v>1.5</v>
@@ -15011,7 +15011,7 @@
         <v>1.51</v>
       </c>
       <c r="DO31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP31" t="b">
         <v>1</v>
@@ -15917,13 +15917,13 @@
         <v>2.01</v>
       </c>
       <c r="DM33" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="DN33" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DO33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP33" t="b">
         <v>1</v>
@@ -16947,12 +16947,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -16968,116 +16968,116 @@
         <v>3</v>
       </c>
       <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>11</v>
+      </c>
+      <c r="L36" t="n">
+        <v>16</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>6</v>
       </c>
-      <c r="K36" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" t="n">
-        <v>9</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="R36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" t="n">
+        <v>11</v>
+      </c>
+      <c r="U36" t="n">
+        <v>14</v>
+      </c>
+      <c r="V36" t="n">
+        <v>18</v>
+      </c>
+      <c r="W36" t="n">
+        <v>14</v>
+      </c>
+      <c r="X36" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Allianz Parque</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD36" t="n">
         <v>4</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>7</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2</v>
-      </c>
-      <c r="S36" t="n">
-        <v>11</v>
-      </c>
-      <c r="T36" t="n">
-        <v>6</v>
-      </c>
-      <c r="U36" t="n">
-        <v>18</v>
-      </c>
-      <c r="V36" t="n">
-        <v>8</v>
-      </c>
-      <c r="W36" t="n">
-        <v>12</v>
-      </c>
-      <c r="X36" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>63</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>37</v>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>Arena do Grêmio</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
-        </is>
-      </c>
-      <c r="AC36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2</v>
-      </c>
       <c r="AE36" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="AF36" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.28</v>
+        <v>4.85</v>
       </c>
       <c r="AH36" t="n">
         <v>1.3</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AK36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN36" t="n">
         <v>1.73</v>
       </c>
-      <c r="AL36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AO36" t="n">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AQ36" t="n">
         <v>1.38</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AT36" t="n">
         <v>1.38</v>
@@ -17086,37 +17086,37 @@
         <v>3</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB36" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="BC36" t="n">
         <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BE36" t="n">
         <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>15714</v>
+        <v>10329</v>
       </c>
       <c r="BG36" t="n">
         <v>2</v>
@@ -17125,139 +17125,139 @@
         <v>1</v>
       </c>
       <c r="BI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ36" t="n">
         <v>5</v>
       </c>
-      <c r="BJ36" t="n">
-        <v>0</v>
-      </c>
       <c r="BK36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM36" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>4</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV36" t="n">
+        <v>46</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>54</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>72</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>103</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CA36" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CB36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="CC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR36" t="n">
+        <v>9</v>
+      </c>
+      <c r="CS36" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU36" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV36" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW36" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX36" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY36" t="n">
         <v>5</v>
-      </c>
-      <c r="BN36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO36" t="n">
-        <v>2</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ36" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS36" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT36" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU36" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV36" t="n">
-        <v>71</v>
-      </c>
-      <c r="BW36" t="n">
-        <v>32</v>
-      </c>
-      <c r="BX36" t="n">
-        <v>126</v>
-      </c>
-      <c r="BY36" t="n">
-        <v>70</v>
-      </c>
-      <c r="BZ36" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CA36" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="CB36" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="CC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS36" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU36" t="n">
-        <v>5</v>
-      </c>
-      <c r="CV36" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW36" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX36" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY36" t="n">
-        <v>7</v>
       </c>
       <c r="CZ36" t="n">
         <v>50</v>
       </c>
       <c r="DA36" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DB36" t="n">
         <v>50</v>
@@ -17266,37 +17266,37 @@
         <v>100</v>
       </c>
       <c r="DD36" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="DE36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF36" t="n">
         <v>3</v>
       </c>
       <c r="DG36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH36" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="DI36" t="n">
-        <v>0.67</v>
+        <v>2.33</v>
       </c>
       <c r="DJ36" t="n">
         <v>50</v>
       </c>
       <c r="DK36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL36" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="DM36" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="DN36" t="n">
-        <v>2.85</v>
+        <v>3.37</v>
       </c>
       <c r="DO36" t="n">
         <v>8</v>
@@ -17324,64 +17324,72 @@
       </c>
       <c r="DW36" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.84</t>
         </is>
       </c>
       <c r="DX36" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="DY36" t="inlineStr">
         <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="DZ36" t="inlineStr"/>
-      <c r="EA36" t="inlineStr"/>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="DZ36" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EA36" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
       <c r="EB36" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="EC36" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="ED36" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EE36" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EF36" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EG36" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="EH36" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EI36" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EJ36" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="EK36" t="inlineStr"/>
@@ -17403,12 +17411,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
@@ -17424,116 +17432,116 @@
         <v>3</v>
       </c>
       <c r="J37" t="n">
+        <v>6</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>9</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>11</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>18</v>
+      </c>
+      <c r="V37" t="n">
+        <v>8</v>
+      </c>
+      <c r="W37" t="n">
+        <v>12</v>
+      </c>
+      <c r="X37" t="n">
         <v>5</v>
       </c>
-      <c r="K37" t="n">
-        <v>11</v>
-      </c>
-      <c r="L37" t="n">
-        <v>16</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="Y37" t="n">
+        <v>63</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Arena do Grêmio</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Bairro Humaitá, Porto Alegre, Rio Grande do Sul</t>
+        </is>
+      </c>
+      <c r="AC37" t="n">
         <v>4</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>6</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>11</v>
-      </c>
-      <c r="U37" t="n">
-        <v>14</v>
-      </c>
-      <c r="V37" t="n">
-        <v>18</v>
-      </c>
-      <c r="W37" t="n">
-        <v>14</v>
-      </c>
-      <c r="X37" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>Allianz Parque</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>Rua Turiaçu 1840, Perdizes, São Paulo, São Paulo</t>
-        </is>
-      </c>
-      <c r="AC37" t="n">
-        <v>3</v>
-      </c>
       <c r="AD37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="AF37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.85</v>
+        <v>3.28</v>
       </c>
       <c r="AH37" t="n">
         <v>1.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AO37" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="AP37" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AQ37" t="n">
         <v>1.38</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AT37" t="n">
         <v>1.38</v>
@@ -17542,37 +17550,37 @@
         <v>3</v>
       </c>
       <c r="AV37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="BC37" t="n">
         <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BE37" t="n">
         <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>10329</v>
+        <v>15714</v>
       </c>
       <c r="BG37" t="n">
         <v>2</v>
@@ -17581,73 +17589,73 @@
         <v>1</v>
       </c>
       <c r="BI37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM37" t="n">
         <v>5</v>
       </c>
-      <c r="BK37" t="n">
+      <c r="BN37" t="n">
         <v>4</v>
       </c>
-      <c r="BL37" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM37" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN37" t="n">
-        <v>8</v>
-      </c>
       <c r="BO37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BP37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ37" t="n">
         <v>2</v>
       </c>
       <c r="BR37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BT37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU37" t="n">
         <v>1</v>
       </c>
       <c r="BV37" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="BW37" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="BX37" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="BY37" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="BZ37" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="CA37" t="n">
-        <v>2.01</v>
+        <v>0.88</v>
       </c>
       <c r="CB37" t="n">
-        <v>3.65</v>
+        <v>3.02</v>
       </c>
       <c r="CC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD37" t="n">
         <v>0</v>
       </c>
       <c r="CE37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF37" t="n">
         <v>0</v>
@@ -17665,55 +17673,55 @@
         <v>1</v>
       </c>
       <c r="CK37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL37" t="n">
         <v>0</v>
       </c>
       <c r="CM37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN37" t="n">
         <v>0</v>
       </c>
       <c r="CO37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ37" t="n">
         <v>1</v>
       </c>
       <c r="CR37" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="CS37" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="CT37" t="n">
         <v>1</v>
       </c>
       <c r="CU37" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="CV37" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW37" t="n">
         <v>1</v>
       </c>
       <c r="CX37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CY37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CZ37" t="n">
         <v>50</v>
       </c>
       <c r="DA37" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB37" t="n">
         <v>50</v>
@@ -17722,37 +17730,37 @@
         <v>100</v>
       </c>
       <c r="DD37" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="DE37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF37" t="n">
         <v>3</v>
       </c>
       <c r="DG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH37" t="n">
-        <v>2.33</v>
+        <v>1</v>
       </c>
       <c r="DI37" t="n">
-        <v>2.33</v>
+        <v>0.67</v>
       </c>
       <c r="DJ37" t="n">
         <v>50</v>
       </c>
       <c r="DK37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL37" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="DM37" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="DN37" t="n">
-        <v>3.37</v>
+        <v>2.85</v>
       </c>
       <c r="DO37" t="n">
         <v>8</v>
@@ -17780,72 +17788,64 @@
       </c>
       <c r="DW37" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="DX37" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="DY37" t="inlineStr">
         <is>
-          <t>5.41</t>
-        </is>
-      </c>
-      <c r="DZ37" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EA37" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="DZ37" t="inlineStr"/>
+      <c r="EA37" t="inlineStr"/>
       <c r="EB37" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC37" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="ED37" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EE37" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EF37" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EG37" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EH37" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI37" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EJ37" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EK37" t="inlineStr"/>
@@ -17897,7 +17897,7 @@
         <v>7</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
@@ -17949,7 +17949,7 @@
         </is>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
         <v>1</v>
@@ -18069,7 +18069,7 @@
         <v>1</v>
       </c>
       <c r="BQ38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR38" t="n">
         <v>0</v>
@@ -18078,7 +18078,7 @@
         <v>2</v>
       </c>
       <c r="BT38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BU38" t="n">
         <v>1</v>
@@ -18345,10 +18345,10 @@
         <v>13</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -18397,10 +18397,10 @@
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="n">
         <v>1.75</v>
@@ -18517,16 +18517,16 @@
         <v>0</v>
       </c>
       <c r="BQ39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS39" t="n">
         <v>0</v>
       </c>
       <c r="BT39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU39" t="n">
         <v>1</v>
@@ -18661,10 +18661,10 @@
         <v>1.87</v>
       </c>
       <c r="DM39" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="DN39" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="DO39" t="n">
         <v>7</v>
@@ -18784,7 +18784,7 @@
         <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -18828,7 +18828,7 @@
         <v>2</v>
       </c>
       <c r="AD40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE40" t="n">
         <v>2.28</v>
@@ -18948,13 +18948,13 @@
         <v>2</v>
       </c>
       <c r="BR40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS40" t="n">
         <v>0</v>
       </c>
       <c r="BT40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU40" t="n">
         <v>1</v>
@@ -21398,13 +21398,13 @@
         <v>25</v>
       </c>
       <c r="DL45" t="n">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="DM45" t="n">
         <v>1.41</v>
       </c>
       <c r="DN45" t="n">
-        <v>4.22</v>
+        <v>4.34</v>
       </c>
       <c r="DO45" t="n">
         <v>8</v>
@@ -21865,10 +21865,10 @@
         <v>1.48</v>
       </c>
       <c r="DM46" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="DN46" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="DO46" t="n">
         <v>7</v>
@@ -23083,31 +23083,31 @@
         <v>5</v>
       </c>
       <c r="BO49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BP49" t="n">
         <v>0</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR49" t="n">
         <v>2</v>
       </c>
       <c r="BS49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BT49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU49" t="n">
         <v>1</v>
       </c>
       <c r="BV49" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BW49" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="BX49" t="n">
         <v>74</v>
@@ -23116,13 +23116,13 @@
         <v>123</v>
       </c>
       <c r="BZ49" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="CB49" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="CC49" t="n">
         <v>0</v>
@@ -23239,7 +23239,7 @@
         <v>2.44</v>
       </c>
       <c r="DO49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23694,13 +23694,13 @@
         <v>50</v>
       </c>
       <c r="DL50" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DM50" t="n">
         <v>1.09</v>
       </c>
       <c r="DN50" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="DO50" t="n">
         <v>7</v>
@@ -23807,104 +23807,96 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
         <v>46096.79166666666</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
+        <v>7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>10</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>14</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>24</v>
+      </c>
+      <c r="V51" t="n">
         <v>4</v>
       </c>
-      <c r="K51" t="n">
-        <v>6</v>
-      </c>
-      <c r="L51" t="n">
-        <v>10</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>4</v>
-      </c>
-      <c r="S51" t="n">
-        <v>8</v>
-      </c>
-      <c r="T51" t="n">
-        <v>6</v>
-      </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
+        <v>13</v>
+      </c>
+      <c r="X51" t="n">
         <v>11</v>
       </c>
-      <c r="V51" t="n">
-        <v>10</v>
-      </c>
-      <c r="W51" t="n">
-        <v>20</v>
-      </c>
-      <c r="X51" t="n">
-        <v>15</v>
-      </c>
       <c r="Y51" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="Z51" t="n">
-        <v>56</v>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>Estádio Urbano Caldeira</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
-        </is>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD51" t="n">
         <v>5</v>
       </c>
-      <c r="AD51" t="n">
-        <v>2</v>
-      </c>
       <c r="AE51" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AF51" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AG51" t="n">
-        <v>3.25</v>
+        <v>4.84</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AI51" t="n">
         <v>2.1</v>
@@ -23913,71 +23905,71 @@
         <v>3.54</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AL51" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AM51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AQ51" t="n">
         <v>1.41</v>
       </c>
-      <c r="AN51" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR51" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AU51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW51" t="n">
         <v>1</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB51" t="n">
+        <v>617</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF51" t="n">
         <v>-1</v>
       </c>
-      <c r="BC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>15008</v>
-      </c>
       <c r="BG51" t="n">
         <v>2</v>
       </c>
@@ -23988,175 +23980,175 @@
         <v>3</v>
       </c>
       <c r="BJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK51" t="n">
         <v>4</v>
       </c>
-      <c r="BK51" t="n">
-        <v>1</v>
-      </c>
       <c r="BL51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV51" t="n">
+        <v>72</v>
+      </c>
+      <c r="BW51" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX51" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY51" t="n">
+        <v>47</v>
+      </c>
+      <c r="BZ51" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CA51" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="CB51" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR51" t="n">
+        <v>14</v>
+      </c>
+      <c r="CS51" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU51" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV51" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW51" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX51" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY51" t="n">
         <v>7</v>
-      </c>
-      <c r="BN51" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ51" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS51" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT51" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU51" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV51" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW51" t="n">
-        <v>33</v>
-      </c>
-      <c r="BX51" t="n">
-        <v>92</v>
-      </c>
-      <c r="BY51" t="n">
-        <v>77</v>
-      </c>
-      <c r="BZ51" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="CA51" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="CB51" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS51" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU51" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV51" t="n">
-        <v>20</v>
-      </c>
-      <c r="CW51" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX51" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY51" t="n">
-        <v>8</v>
       </c>
       <c r="CZ51" t="n">
         <v>25</v>
       </c>
       <c r="DA51" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DB51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DC51" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="DE51" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="DF51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="DG51" t="n">
         <v>2</v>
       </c>
       <c r="DH51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DI51" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="DJ51" t="n">
         <v>75</v>
       </c>
       <c r="DK51" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DL51" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="DM51" t="n">
-        <v>0.44</v>
+        <v>1.3</v>
       </c>
       <c r="DN51" t="n">
-        <v>1.56</v>
+        <v>2.57</v>
       </c>
       <c r="DO51" t="n">
         <v>8</v>
@@ -24168,13 +24160,13 @@
         <v>1</v>
       </c>
       <c r="DR51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU51" t="b">
         <v>0</v>
@@ -24184,76 +24176,84 @@
       </c>
       <c r="DW51" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="DX51" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="DY51" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="DZ51" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EA51" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EB51" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EC51" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="ED51" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EE51" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EF51" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EG51" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EH51" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EI51" t="inlineStr">
         <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EJ51" t="inlineStr">
+        <is>
+          <t>2.86</t>
+        </is>
+      </c>
+      <c r="EK51" t="inlineStr">
+        <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="EJ51" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="EK51" t="inlineStr"/>
-      <c r="EL51" t="inlineStr"/>
+      <c r="EL51" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -24271,96 +24271,104 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>46096.79166666666</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
+        <v>10</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4</v>
+      </c>
+      <c r="S52" t="n">
         <v>8</v>
       </c>
-      <c r="M52" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
+      <c r="T52" t="n">
+        <v>6</v>
+      </c>
+      <c r="U52" t="n">
+        <v>11</v>
+      </c>
+      <c r="V52" t="n">
         <v>10</v>
       </c>
-      <c r="R52" t="n">
-        <v>2</v>
-      </c>
-      <c r="S52" t="n">
-        <v>14</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2</v>
-      </c>
-      <c r="U52" t="n">
-        <v>24</v>
-      </c>
-      <c r="V52" t="n">
+      <c r="W52" t="n">
+        <v>20</v>
+      </c>
+      <c r="X52" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>56</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Estádio Urbano Caldeira</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Rue Princesa Isabel 77, Vila Belmiro, Santos, São Paulo</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
         <v>4</v>
       </c>
-      <c r="W52" t="n">
-        <v>13</v>
-      </c>
-      <c r="X52" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="n">
-        <v>2</v>
-      </c>
       <c r="AD52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AF52" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AG52" t="n">
-        <v>4.84</v>
+        <v>3.25</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AI52" t="n">
         <v>2.1</v>
@@ -24369,253 +24377,253 @@
         <v>3.54</v>
       </c>
       <c r="AK52" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AL52" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AO52" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AU52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>15008</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>33</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>92</v>
+      </c>
+      <c r="BY52" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ52" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CA52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CB52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO52" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR52" t="n">
+        <v>18</v>
+      </c>
+      <c r="CS52" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU52" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV52" t="n">
+        <v>20</v>
+      </c>
+      <c r="CW52" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX52" t="n">
         <v>5</v>
       </c>
-      <c r="AV52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>617</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI52" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK52" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM52" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN52" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR52" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS52" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT52" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV52" t="n">
-        <v>72</v>
-      </c>
-      <c r="BW52" t="n">
-        <v>15</v>
-      </c>
-      <c r="BX52" t="n">
-        <v>118</v>
-      </c>
-      <c r="BY52" t="n">
-        <v>47</v>
-      </c>
-      <c r="BZ52" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="CA52" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="CB52" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="CC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP52" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS52" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU52" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV52" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW52" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX52" t="n">
-        <v>4</v>
-      </c>
       <c r="CY52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CZ52" t="n">
         <v>25</v>
       </c>
       <c r="DA52" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DB52" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DC52" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DF52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG52" t="n">
         <v>2</v>
       </c>
       <c r="DH52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DI52" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DJ52" t="n">
         <v>75</v>
       </c>
       <c r="DK52" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DL52" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="DM52" t="n">
-        <v>1.3</v>
+        <v>0.44</v>
       </c>
       <c r="DN52" t="n">
-        <v>2.57</v>
+        <v>1.56</v>
       </c>
       <c r="DO52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -24624,13 +24632,13 @@
         <v>1</v>
       </c>
       <c r="DR52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU52" t="b">
         <v>0</v>
@@ -24640,84 +24648,76 @@
       </c>
       <c r="DW52" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="DX52" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="DY52" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="DZ52" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EA52" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EB52" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="EC52" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="ED52" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EE52" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EF52" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EG52" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="EH52" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EI52" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EJ52" t="inlineStr">
         <is>
-          <t>2.86</t>
-        </is>
-      </c>
-      <c r="EK52" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EL52" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="EK52" t="inlineStr"/>
+      <c r="EL52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -26121,10 +26121,10 @@
         <v>9</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -26173,10 +26173,10 @@
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE56" t="n">
         <v>1.88</v>
@@ -26293,16 +26293,16 @@
         <v>1</v>
       </c>
       <c r="BQ56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS56" t="n">
         <v>1</v>
       </c>
       <c r="BT56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU56" t="n">
         <v>1</v>
@@ -26599,10 +26599,10 @@
         <v>13</v>
       </c>
       <c r="W57" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y57" t="n">
         <v>35</v>
@@ -26882,13 +26882,13 @@
         <v>0</v>
       </c>
       <c r="DL57" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="DM57" t="n">
         <v>0.91</v>
       </c>
       <c r="DN57" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="DO57" t="n">
         <v>7</v>
@@ -27492,7 +27492,7 @@
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -27544,7 +27544,7 @@
         <v>1</v>
       </c>
       <c r="AD59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE59" t="n">
         <v>1.55</v>
@@ -27664,13 +27664,13 @@
         <v>1</v>
       </c>
       <c r="BR59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS59" t="n">
         <v>1</v>
       </c>
       <c r="BT59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU59" t="n">
         <v>1</v>
@@ -27781,7 +27781,7 @@
         <v>3</v>
       </c>
       <c r="DE59" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF59" t="n">
         <v>3</v>
@@ -27811,7 +27811,7 @@
         <v>2.4</v>
       </c>
       <c r="DO59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP59" t="b">
         <v>1</v>
@@ -28226,7 +28226,7 @@
         <v>84</v>
       </c>
       <c r="DD60" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DE60" t="n">
         <v>0.25</v>
@@ -28259,7 +28259,7 @@
         <v>2.96</v>
       </c>
       <c r="DO60" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29618,13 +29618,13 @@
         <v>17</v>
       </c>
       <c r="DL63" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="DM63" t="n">
         <v>1.75</v>
       </c>
       <c r="DN63" t="n">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="DO63" t="n">
         <v>8</v>
@@ -30458,7 +30458,7 @@
         <v>17</v>
       </c>
       <c r="CV65" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CW65" t="n">
         <v>1</v>
@@ -31402,13 +31402,13 @@
         <v>17</v>
       </c>
       <c r="DL67" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DM67" t="n">
         <v>0.68</v>
       </c>
       <c r="DN67" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="DO67" t="n">
         <v>7</v>
@@ -31813,7 +31813,7 @@
         <v>1</v>
       </c>
       <c r="DE68" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DF68" t="n">
         <v>1.33</v>
@@ -31843,7 +31843,7 @@
         <v>2.16</v>
       </c>
       <c r="DO68" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -33205,10 +33205,10 @@
         <v>1.58</v>
       </c>
       <c r="DM71" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="DN71" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="DO71" t="n">
         <v>8</v>
@@ -34090,7 +34090,7 @@
         <v>88</v>
       </c>
       <c r="DD73" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DE73" t="n">
         <v>2</v>
@@ -34123,7 +34123,7 @@
         <v>2.52</v>
       </c>
       <c r="DO73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -34570,13 +34570,13 @@
         <v>13</v>
       </c>
       <c r="DL74" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DM74" t="n">
         <v>1.04</v>
       </c>
       <c r="DN74" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="DO74" t="n">
         <v>8</v>
@@ -35018,13 +35018,13 @@
         <v>34</v>
       </c>
       <c r="DL75" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DM75" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DO75" t="n">
         <v>7</v>
@@ -35941,10 +35941,10 @@
         <v>1.36</v>
       </c>
       <c r="DM77" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="DN77" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="DO77" t="n">
         <v>7</v>
@@ -36034,6 +36034,446 @@
           <t>2.25</t>
         </is>
       </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Brasileirão_Série_A_2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Atlético PR</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>46110.9375</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>8</v>
+      </c>
+      <c r="L78" t="n">
+        <v>9</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>8</v>
+      </c>
+      <c r="R78" t="n">
+        <v>3</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="n">
+        <v>9</v>
+      </c>
+      <c r="U78" t="n">
+        <v>11</v>
+      </c>
+      <c r="V78" t="n">
+        <v>12</v>
+      </c>
+      <c r="W78" t="n">
+        <v>13</v>
+      </c>
+      <c r="X78" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>622</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>22625</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV78" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX78" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY78" t="n">
+        <v>4</v>
+      </c>
+      <c r="CZ78" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA78" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB78" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC78" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DE78" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DF78" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH78" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DI78" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK78" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="DM78" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DN78" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="DO78" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DU78" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV78" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW78" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="DX78" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="DY78" t="inlineStr">
+        <is>
+          <t>4.12</t>
+        </is>
+      </c>
+      <c r="DZ78" t="inlineStr"/>
+      <c r="EA78" t="inlineStr"/>
+      <c r="EB78" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EC78" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EE78" t="inlineStr"/>
+      <c r="EF78" t="inlineStr"/>
+      <c r="EG78" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr"/>
+      <c r="EL78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -42104,7 +42104,7 @@
         <v>0</v>
       </c>
       <c r="BF91" t="n">
-        <v>-1</v>
+        <v>20072</v>
       </c>
       <c r="BG91" t="n">
         <v>2</v>
@@ -43000,7 +43000,7 @@
         <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>-1</v>
+        <v>68615</v>
       </c>
       <c r="BG93" t="n">
         <v>2</v>
@@ -43432,7 +43432,7 @@
         <v>0</v>
       </c>
       <c r="BF94" t="n">
-        <v>-1</v>
+        <v>29356</v>
       </c>
       <c r="BG94" t="n">
         <v>2</v>
@@ -43880,7 +43880,7 @@
         <v>0</v>
       </c>
       <c r="BF95" t="n">
-        <v>-1</v>
+        <v>41387</v>
       </c>
       <c r="BG95" t="n">
         <v>2</v>
@@ -44336,7 +44336,7 @@
         <v>0</v>
       </c>
       <c r="BF96" t="n">
-        <v>-1</v>
+        <v>32213</v>
       </c>
       <c r="BG96" t="n">
         <v>2</v>
@@ -44776,7 +44776,7 @@
         <v>0</v>
       </c>
       <c r="BF97" t="n">
-        <v>-1</v>
+        <v>3597</v>
       </c>
       <c r="BG97" t="n">
         <v>2</v>
@@ -44911,7 +44911,7 @@
         <v>7</v>
       </c>
       <c r="CY97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ97" t="n">
         <v>38</v>
@@ -45333,7 +45333,7 @@
         <v>22</v>
       </c>
       <c r="CS98" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CT98" t="n">
         <v>1</v>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -68293,7 +68293,7 @@
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R150" t="n">
         <v>3</v>
@@ -68305,7 +68305,7 @@
         <v>4</v>
       </c>
       <c r="U150" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V150" t="n">
         <v>7</v>
@@ -68412,7 +68412,7 @@
         <v>0</v>
       </c>
       <c r="BF150" t="n">
-        <v>-1</v>
+        <v>20027</v>
       </c>
       <c r="BG150" t="n">
         <v>2</v>
@@ -68472,13 +68472,13 @@
         <v>76</v>
       </c>
       <c r="BZ150" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="CA150" t="n">
         <v>0.99</v>
       </c>
       <c r="CB150" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="CC150" t="n">
         <v>1</v>
@@ -68844,7 +68844,7 @@
         <v>0</v>
       </c>
       <c r="BF151" t="n">
-        <v>-1</v>
+        <v>28218</v>
       </c>
       <c r="BG151" t="n">
         <v>2</v>
@@ -69292,7 +69292,7 @@
         <v>0</v>
       </c>
       <c r="BF152" t="n">
-        <v>-1</v>
+        <v>27657</v>
       </c>
       <c r="BG152" t="n">
         <v>2</v>
@@ -70069,10 +70069,10 @@
         <v>14</v>
       </c>
       <c r="Y154" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Z154" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
@@ -70172,7 +70172,7 @@
         <v>0</v>
       </c>
       <c r="BF154" t="n">
-        <v>-1</v>
+        <v>26800</v>
       </c>
       <c r="BG154" t="n">
         <v>2</v>
@@ -70966,13 +70966,13 @@
         <v>18</v>
       </c>
       <c r="T156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U156" t="n">
         <v>23</v>
       </c>
       <c r="V156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W156" t="n">
         <v>21</v>
@@ -70981,10 +70981,10 @@
         <v>11</v>
       </c>
       <c r="Y156" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Z156" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr"/>
@@ -71076,7 +71076,7 @@
         <v>0</v>
       </c>
       <c r="BF156" t="n">
-        <v>34197</v>
+        <v>1793</v>
       </c>
       <c r="BG156" t="n">
         <v>2</v>
@@ -71139,10 +71139,10 @@
         <v>2.31</v>
       </c>
       <c r="CA156" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="CB156" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="CC156" t="n">
         <v>1</v>
@@ -71190,7 +71190,7 @@
         <v>1</v>
       </c>
       <c r="CR156" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CS156" t="n">
         <v>14</v>
@@ -71516,7 +71516,7 @@
         <v>0</v>
       </c>
       <c r="BF157" t="n">
-        <v>-1</v>
+        <v>9202</v>
       </c>
       <c r="BG157" t="n">
         <v>2</v>

--- a/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
+++ b/data/matches/leagues/Brasileirão_Série_A_2026.xlsx
@@ -75916,7 +75916,7 @@
         <v>0</v>
       </c>
       <c r="BF169" t="n">
-        <v>-1</v>
+        <v>51270</v>
       </c>
       <c r="BG169" t="n">
         <v>2</v>
@@ -76137,19 +76137,23 @@
           <t>9.42</t>
         </is>
       </c>
-      <c r="DZ169" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="EA169" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
-      </c>
-      <c r="EB169" t="inlineStr"/>
-      <c r="EC169" t="inlineStr"/>
-      <c r="ED169" t="inlineStr"/>
+      <c r="DZ169" t="inlineStr"/>
+      <c r="EA169" t="inlineStr"/>
+      <c r="EB169" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EC169" t="inlineStr">
+        <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="ED169" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
       <c r="EE169" t="inlineStr"/>
       <c r="EF169" t="inlineStr"/>
       <c r="EG169" t="inlineStr">
@@ -76172,16 +76176,8 @@
           <t>3.34</t>
         </is>
       </c>
-      <c r="EK169" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EL169" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
+      <c r="EK169" t="inlineStr"/>
+      <c r="EL169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -76581,16 +76577,8 @@
           <t>4.47</t>
         </is>
       </c>
-      <c r="DZ170" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="EA170" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+      <c r="DZ170" t="inlineStr"/>
+      <c r="EA170" t="inlineStr"/>
       <c r="EB170" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -77029,16 +77017,8 @@
           <t>2.50</t>
         </is>
       </c>
-      <c r="DZ171" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
-      <c r="EA171" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
+      <c r="DZ171" t="inlineStr"/>
+      <c r="EA171" t="inlineStr"/>
       <c r="EB171" t="inlineStr">
         <is>
           <t>1.40</t>
@@ -77056,36 +77036,12 @@
       </c>
       <c r="EE171" t="inlineStr"/>
       <c r="EF171" t="inlineStr"/>
-      <c r="EG171" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="EH171" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="EI171" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EJ171" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="EK171" t="inlineStr">
-        <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EL171" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
+      <c r="EG171" t="inlineStr"/>
+      <c r="EH171" t="inlineStr"/>
+      <c r="EI171" t="inlineStr"/>
+      <c r="EJ171" t="inlineStr"/>
+      <c r="EK171" t="inlineStr"/>
+      <c r="EL171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -77696,7 +77652,7 @@
         <v>0</v>
       </c>
       <c r="BF173" t="n">
-        <v>-1</v>
+        <v>11172</v>
       </c>
       <c r="BG173" t="n">
         <v>2</v>
@@ -77917,8 +77873,16 @@
           <t>5.73</t>
         </is>
       </c>
-      <c r="DZ173" t="inlineStr"/>
-      <c r="EA173" t="inlineStr"/>
+      <c r="DZ173" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EA173" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
       <c r="EB173" t="inlineStr">
         <is>
           <t>1.30</t>
@@ -77936,10 +77900,26 @@
       </c>
       <c r="EE173" t="inlineStr"/>
       <c r="EF173" t="inlineStr"/>
-      <c r="EG173" t="inlineStr"/>
-      <c r="EH173" t="inlineStr"/>
-      <c r="EI173" t="inlineStr"/>
-      <c r="EJ173" t="inlineStr"/>
+      <c r="EG173" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="EH173" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="EI173" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EJ173" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
       <c r="EK173" t="inlineStr"/>
       <c r="EL173" t="inlineStr"/>
     </row>
@@ -78120,7 +78100,7 @@
         <v>0</v>
       </c>
       <c r="BF174" t="n">
-        <v>-1</v>
+        <v>5474</v>
       </c>
       <c r="BG174" t="n">
         <v>2</v>
@@ -78368,10 +78348,26 @@
       </c>
       <c r="EE174" t="inlineStr"/>
       <c r="EF174" t="inlineStr"/>
-      <c r="EG174" t="inlineStr"/>
-      <c r="EH174" t="inlineStr"/>
-      <c r="EI174" t="inlineStr"/>
-      <c r="EJ174" t="inlineStr"/>
+      <c r="EG174" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EH174" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EI174" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EJ174" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
       <c r="EK174" t="inlineStr"/>
       <c r="EL174" t="inlineStr"/>
     </row>
@@ -78552,7 +78548,7 @@
         <v>0</v>
       </c>
       <c r="BF175" t="n">
-        <v>-1</v>
+        <v>36543</v>
       </c>
       <c r="BG175" t="n">
         <v>2</v>
@@ -78992,7 +78988,7 @@
         <v>0</v>
       </c>
       <c r="BF176" t="n">
-        <v>-1</v>
+        <v>20133</v>
       </c>
       <c r="BG176" t="n">
         <v>2</v>
@@ -79213,16 +79209,8 @@
           <t>4.22</t>
         </is>
       </c>
-      <c r="DZ176" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="EA176" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+      <c r="DZ176" t="inlineStr"/>
+      <c r="EA176" t="inlineStr"/>
       <c r="EB176" t="inlineStr">
         <is>
           <t>1.33</t>
@@ -79244,16 +79232,8 @@
       <c r="EH176" t="inlineStr"/>
       <c r="EI176" t="inlineStr"/>
       <c r="EJ176" t="inlineStr"/>
-      <c r="EK176" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EL176" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
+      <c r="EK176" t="inlineStr"/>
+      <c r="EL176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -79432,7 +79412,7 @@
         <v>0</v>
       </c>
       <c r="BF177" t="n">
-        <v>-1</v>
+        <v>29662</v>
       </c>
       <c r="BG177" t="n">
         <v>2</v>
@@ -79793,10 +79773,10 @@
         <v>14</v>
       </c>
       <c r="Y178" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z178" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -79888,7 +79868,7 @@
         <v>0</v>
       </c>
       <c r="BF178" t="n">
-        <v>-1</v>
+        <v>25649</v>
       </c>
       <c r="BG178" t="n">
         <v>2</v>
